--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_11_36.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_11_36.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3284135.583634978</v>
+        <v>3246468.48316955</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8185132.877801319</v>
+        <v>8185132.877801191</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8185132.877801319</v>
+        <v>8185132.877801191</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4915137.860185931</v>
+        <v>4912460.722152626</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4915137.860185931</v>
+        <v>4912460.722152626</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>54663083.08557065</v>
+        <v>54656545.05935857</v>
       </c>
     </row>
   </sheetData>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.99931295557451</v>
+        <v>481.9993129555745</v>
       </c>
       <c r="C2" t="n">
         <v>49.47457824299391</v>
@@ -663,13 +663,13 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E2" t="n">
-        <v>404.3632896068686</v>
+        <v>15.85984911447004</v>
       </c>
       <c r="F2" t="n">
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>403.5603873623931</v>
+        <v>3.560387362393101</v>
       </c>
       <c r="H2" t="n">
         <v>5.992286844230932</v>
@@ -681,19 +681,19 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>44.06766137137288</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>130.3937811045784</v>
       </c>
       <c r="M2" t="n">
-        <v>211.5195683314804</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>37.05812585549948</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>238.5047445569377</v>
       </c>
       <c r="S2" t="n">
-        <v>490.3593738324736</v>
+        <v>90.35937383247364</v>
       </c>
       <c r="T2" t="n">
         <v>185.8132802210262</v>
@@ -720,10 +720,10 @@
         <v>238.3734759809475</v>
       </c>
       <c r="X2" t="n">
-        <v>442.2831375252067</v>
+        <v>592.2818334606677</v>
       </c>
       <c r="Y2" t="n">
-        <v>111.3174326828064</v>
+        <v>511.3174326828064</v>
       </c>
     </row>
     <row r="3">
@@ -736,7 +736,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -748,13 +748,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>239.747545602538</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>213.4976123064429</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -790,7 +790,7 @@
         <v>4.932944462796854</v>
       </c>
       <c r="U3" t="n">
-        <v>92.34867126138433</v>
+        <v>400.2034257979226</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -799,7 +799,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
-        <v>419.8627394453875</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -891,37 +891,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>235.9827708393279</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C5" t="n">
         <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
-        <v>410.3391557398498</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E5" t="n">
         <v>404.3632896068686</v>
       </c>
       <c r="F5" t="n">
-        <v>4.889628708011855</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G5" t="n">
-        <v>3.560387362393095</v>
+        <v>403.5603873623931</v>
       </c>
       <c r="H5" t="n">
         <v>5.992286844230925</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>142.486898376152</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>44.06766137137288</v>
+        <v>211.5195683314564</v>
       </c>
       <c r="L5" t="n">
-        <v>167.4519069601296</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>238.5047445569377</v>
       </c>
       <c r="S5" t="n">
-        <v>90.35937383247366</v>
+        <v>101.8559333400752</v>
       </c>
       <c r="T5" t="n">
-        <v>585.8132802210262</v>
+        <v>185.8132802210262</v>
       </c>
       <c r="U5" t="n">
         <v>249.2055377546408</v>
@@ -970,13 +970,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>251.7707747048845</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>140.7299859716246</v>
       </c>
       <c r="S6" t="n">
-        <v>64.60631128536602</v>
+        <v>464.606311285366</v>
       </c>
       <c r="T6" t="n">
         <v>4.932944462796835</v>
@@ -1030,13 +1030,13 @@
         <v>0.2034257979225968</v>
       </c>
       <c r="V6" t="n">
-        <v>414.5106671915202</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
         <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>248.1768699494648</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E8" t="n">
-        <v>404.3632896068686</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F8" t="n">
-        <v>254.8909327725508</v>
+        <v>16.38618821561328</v>
       </c>
       <c r="G8" t="n">
         <v>3.560387362393095</v>
       </c>
       <c r="H8" t="n">
-        <v>5.992286844230925</v>
+        <v>405.9922868442309</v>
       </c>
       <c r="I8" t="n">
         <v>142.486898376152</v>
@@ -1155,10 +1155,10 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>44.06766137137285</v>
       </c>
       <c r="L8" t="n">
-        <v>211.519568331518</v>
+        <v>71.83897161868299</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1167,7 +1167,7 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>95.61293534150843</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1176,10 +1176,10 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>238.5047445569377</v>
       </c>
       <c r="S8" t="n">
-        <v>490.3593738324736</v>
+        <v>90.35937383247366</v>
       </c>
       <c r="T8" t="n">
         <v>185.8132802210262</v>
@@ -1191,7 +1191,7 @@
         <v>229.8510241668239</v>
       </c>
       <c r="W8" t="n">
-        <v>238.3734759809475</v>
+        <v>638.3734759809475</v>
       </c>
       <c r="X8" t="n">
         <v>192.2818334606677</v>
@@ -1213,22 +1213,22 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>287.2365475017917</v>
       </c>
       <c r="F9" t="n">
-        <v>51.4353879462584</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.6341396486122</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>213.4976123064429</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1255,13 +1255,13 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>140.7299859716246</v>
+        <v>540.7299859716246</v>
       </c>
       <c r="S9" t="n">
         <v>64.60631128536602</v>
       </c>
       <c r="T9" t="n">
-        <v>404.9329444627969</v>
+        <v>4.932944462796835</v>
       </c>
       <c r="U9" t="n">
         <v>0.2034257979225968</v>
@@ -1380,7 +1380,7 @@
         <v>187.8896287080119</v>
       </c>
       <c r="G11" t="n">
-        <v>186.5603873623931</v>
+        <v>3.031216461454802</v>
       </c>
       <c r="H11" t="n">
         <v>188.9922868442309</v>
@@ -1419,22 +1419,22 @@
         <v>273.3593738324736</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>368.8132802210262</v>
       </c>
       <c r="U11" t="n">
-        <v>432.2055377546408</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>84.96519495440994</v>
+        <v>412.8510241668239</v>
       </c>
       <c r="W11" t="n">
         <v>421.3734759809475</v>
       </c>
       <c r="X11" t="n">
-        <v>375.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>294.3174326828064</v>
       </c>
     </row>
     <row r="12">
@@ -1602,25 +1602,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>242.9993129555745</v>
+        <v>243.9993129555745</v>
       </c>
       <c r="C14" t="n">
-        <v>210.4745782429939</v>
+        <v>211.4745782429939</v>
       </c>
       <c r="D14" t="n">
-        <v>171.3391557398498</v>
+        <v>172.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>165.3632896068686</v>
+        <v>166.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>165.8896287080119</v>
+        <v>166.8896287080119</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>165.5603873623931</v>
       </c>
       <c r="H14" t="n">
-        <v>166.9922868442309</v>
+        <v>167.9922868442309</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1650,28 +1650,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>0.5047445569376805</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>252.3593738324737</v>
       </c>
       <c r="T14" t="n">
-        <v>346.8132802210262</v>
+        <v>347.8132802210262</v>
       </c>
       <c r="U14" t="n">
-        <v>410.2055377546408</v>
+        <v>411.2055377546408</v>
       </c>
       <c r="V14" t="n">
-        <v>390.8510241668239</v>
+        <v>116.2079580315243</v>
       </c>
       <c r="W14" t="n">
-        <v>399.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>353.2818334606677</v>
+        <v>354.2818334606677</v>
       </c>
       <c r="Y14" t="n">
-        <v>26.72539631836385</v>
+        <v>273.3174326828064</v>
       </c>
     </row>
     <row r="15">
@@ -1681,25 +1681,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>145.5565566463266</v>
+        <v>146.5565566463266</v>
       </c>
       <c r="C15" t="n">
-        <v>122.0999124455193</v>
+        <v>123.0999124455193</v>
       </c>
       <c r="D15" t="n">
-        <v>108.9376868977026</v>
+        <v>109.9376868977026</v>
       </c>
       <c r="E15" t="n">
-        <v>103.6720972219126</v>
+        <v>104.6720972219126</v>
       </c>
       <c r="F15" t="n">
-        <v>100.6362423378769</v>
+        <v>101.6362423378769</v>
       </c>
       <c r="G15" t="n">
-        <v>86.63413964861225</v>
+        <v>87.63413964861225</v>
       </c>
       <c r="H15" t="n">
-        <v>92.15018152604378</v>
+        <v>93.15018152604378</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1729,28 +1729,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>301.7299859716246</v>
+        <v>302.7299859716246</v>
       </c>
       <c r="S15" t="n">
-        <v>225.606311285366</v>
+        <v>226.606311285366</v>
       </c>
       <c r="T15" t="n">
-        <v>165.9329444627968</v>
+        <v>166.9329444627968</v>
       </c>
       <c r="U15" t="n">
-        <v>161.2034257979226</v>
+        <v>162.2034257979226</v>
       </c>
       <c r="V15" t="n">
-        <v>175.5106671915202</v>
+        <v>176.5106671915202</v>
       </c>
       <c r="W15" t="n">
-        <v>193.3731429098285</v>
+        <v>194.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>180.8627394453875</v>
+        <v>181.8627394453875</v>
       </c>
       <c r="Y15" t="n">
-        <v>160.3913927661343</v>
+        <v>161.3913927661343</v>
       </c>
     </row>
     <row r="16">
@@ -1763,13 +1763,13 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33.72524664804467</v>
+        <v>34.72524664804467</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>41.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1802,16 +1802,16 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>192.3520920692644</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>395.7712442126372</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>121.8335944569538</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1826,10 +1826,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>8.443645430107551</v>
+        <v>9.443645430107551</v>
       </c>
       <c r="Y16" t="n">
-        <v>48.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>200.8475762731646</v>
+        <v>204.3593738324737</v>
       </c>
       <c r="T17" t="n">
         <v>299.8132802210262</v>
@@ -1899,7 +1899,7 @@
         <v>363.2055377546408</v>
       </c>
       <c r="V17" t="n">
-        <v>343.8510241668239</v>
+        <v>340.339226607515</v>
       </c>
       <c r="W17" t="n">
         <v>352.3734759809475</v>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.113800337078658</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -2030,25 +2030,25 @@
         <v>124.410808485648</v>
       </c>
       <c r="M19" t="n">
-        <v>220.7806769763204</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>271.6634851077505</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>22.96287247848491</v>
       </c>
       <c r="P19" t="n">
-        <v>105.8862859603386</v>
+        <v>390.7610776561463</v>
       </c>
       <c r="Q19" t="n">
-        <v>432.440266425598</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>74.83359445695379</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>56.12784860405002</v>
+        <v>74.50182585550775</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>341.9561870298346</v>
       </c>
       <c r="P22" t="n">
         <v>390.7610776561463</v>
@@ -2282,10 +2282,10 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>436.6291115877084</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>74.83359445695379</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.465352849462363</v>
       </c>
     </row>
     <row r="23">
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.113800337078658</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -2510,19 +2510,19 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>341.9561870298346</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>390.7610776561463</v>
       </c>
       <c r="Q25" t="n">
-        <v>372.0553318032426</v>
+        <v>151.9145734990025</v>
       </c>
       <c r="R25" t="n">
-        <v>436.6291115877084</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>74.83359445695379</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2550,25 +2550,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>264.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>232.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>193.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>187.3632896068686</v>
+        <v>58.89216800687643</v>
       </c>
       <c r="F26" t="n">
-        <v>187.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>186.5603873623931</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>188.9922868442309</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2598,16 +2598,16 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>21.50474455693768</v>
       </c>
       <c r="S26" t="n">
-        <v>273.3593738324736</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>368.8132802210262</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>432.2055377546408</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>412.8510241668239</v>
@@ -2616,10 +2616,10 @@
         <v>421.3734759809475</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>375.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>180.1704023668139</v>
+        <v>294.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -2644,7 +2644,7 @@
         <v>122.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>104.9231130940376</v>
+        <v>108.6341396486122</v>
       </c>
       <c r="H27" t="n">
         <v>114.1501815260438</v>
@@ -2677,7 +2677,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>323.7299859716246</v>
+        <v>320.0189594171518</v>
       </c>
       <c r="S27" t="n">
         <v>247.606311285366</v>
@@ -2744,7 +2744,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>304.8331153747783</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>224.9949526866063</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -2771,13 +2771,13 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>9.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>70.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2787,19 +2787,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>204.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
         <v>172.4745782429939</v>
       </c>
       <c r="D29" t="n">
-        <v>47.27642034921999</v>
+        <v>133.3391557398498</v>
       </c>
       <c r="E29" t="n">
         <v>127.3632896068686</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>127.8896287080119</v>
       </c>
       <c r="G29" t="n">
         <v>126.5603873623931</v>
@@ -2850,10 +2850,10 @@
         <v>352.8510241668239</v>
       </c>
       <c r="W29" t="n">
-        <v>361.3734759809475</v>
+        <v>37.13859137725683</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>315.2818334606677</v>
       </c>
       <c r="Y29" t="n">
         <v>234.3174326828064</v>
@@ -2945,16 +2945,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>8.53621805555548</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>3.98090483695654</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -2978,16 +2978,16 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>229.7806769763204</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>86.7102590811725</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>235.0606641559725</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -2996,7 +2996,7 @@
         <v>445.6291115877085</v>
       </c>
       <c r="S31" t="n">
-        <v>83.83359445695379</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3030,19 +3030,19 @@
         <v>172.4745782429939</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>133.3391557398498</v>
       </c>
       <c r="E32" t="n">
-        <v>127.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>127.8896287080119</v>
       </c>
       <c r="G32" t="n">
-        <v>126.5603873623931</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>128.9922868442309</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3084,13 +3084,13 @@
         <v>372.2055377546408</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>352.8510241668239</v>
       </c>
       <c r="W32" t="n">
-        <v>318.3294583283118</v>
+        <v>361.3734759809475</v>
       </c>
       <c r="X32" t="n">
-        <v>315.2818334606677</v>
+        <v>168.9635997149242</v>
       </c>
       <c r="Y32" t="n">
         <v>234.3174326828064</v>
@@ -3188,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>8.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -3215,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>229.7806769763204</v>
       </c>
       <c r="N34" t="n">
         <v>280.6634851077505</v>
@@ -3224,16 +3224,16 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>254.0792081165638</v>
       </c>
       <c r="Q34" t="n">
-        <v>391.4900725803749</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>83.83359445695379</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>204.9993129555745</v>
       </c>
       <c r="C35" t="n">
-        <v>172.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>133.3391557398498</v>
@@ -3276,7 +3276,7 @@
         <v>127.8896287080119</v>
       </c>
       <c r="G35" t="n">
-        <v>117.6073362193261</v>
+        <v>126.5603873623931</v>
       </c>
       <c r="H35" t="n">
         <v>128.9922868442309</v>
@@ -3312,13 +3312,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>213.3593738324736</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
         <v>308.8132802210262</v>
       </c>
       <c r="U35" t="n">
-        <v>372.2055377546408</v>
+        <v>228.8052922709012</v>
       </c>
       <c r="V35" t="n">
         <v>352.8510241668239</v>
@@ -3327,7 +3327,7 @@
         <v>361.3734759809475</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>315.2818334606677</v>
       </c>
       <c r="Y35" t="n">
         <v>234.3174326828064</v>
@@ -3419,16 +3419,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>10.11380033707866</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>8.53621805555548</v>
       </c>
       <c r="E37" t="n">
-        <v>3.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -3455,16 +3455,16 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>9.473648165313696</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>350.9561870298346</v>
       </c>
       <c r="P37" t="n">
-        <v>399.7610776561463</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>405.0309651152447</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -3488,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>10.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>204.9993129555745</v>
+        <v>120.0392357012658</v>
       </c>
       <c r="C38" t="n">
         <v>172.4745782429939</v>
@@ -3549,13 +3549,13 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>213.3593738324737</v>
+        <v>213.3593738324736</v>
       </c>
       <c r="T38" t="n">
         <v>308.8132802210262</v>
       </c>
       <c r="U38" t="n">
-        <v>287.24546050023</v>
+        <v>372.2055377546408</v>
       </c>
       <c r="V38" t="n">
         <v>352.8510241668239</v>
@@ -3592,10 +3592,10 @@
         <v>62.63624233787687</v>
       </c>
       <c r="G39" t="n">
-        <v>48.63413964861225</v>
+        <v>48.63413964861223</v>
       </c>
       <c r="H39" t="n">
-        <v>54.15018152604377</v>
+        <v>54.15018152604375</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3631,7 +3631,7 @@
         <v>187.606311285366</v>
       </c>
       <c r="T39" t="n">
-        <v>127.9329444627968</v>
+        <v>127.9329444627969</v>
       </c>
       <c r="U39" t="n">
         <v>123.2034257979226</v>
@@ -3662,7 +3662,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>8.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -3683,25 +3683,25 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>1.254872161798801</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>229.7806769763204</v>
       </c>
       <c r="N40" t="n">
-        <v>230.3617387501437</v>
+        <v>280.6634851077505</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>168.6391889854275</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>441.440266425598</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>92.57296965837392</v>
       </c>
       <c r="C41" t="n">
-        <v>320.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -3750,13 +3750,13 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>274.5603873623931</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>276.9922868442309</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>13.48689837615194</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3783,28 +3783,28 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>109.5047445569377</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>361.3593738324736</v>
       </c>
       <c r="T41" t="n">
-        <v>5.370564185228964</v>
+        <v>456.8132802210262</v>
       </c>
       <c r="U41" t="n">
-        <v>520.2055377546408</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>500.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>509.3734759809475</v>
       </c>
       <c r="X41" t="n">
         <v>463.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>382.3174326828064</v>
       </c>
     </row>
     <row r="42">
@@ -3817,25 +3817,25 @@
         <v>255.5565566463266</v>
       </c>
       <c r="C42" t="n">
-        <v>136.4479171116598</v>
+        <v>232.0999124455193</v>
       </c>
       <c r="D42" t="n">
         <v>218.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>213.6720972219126</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>196.6341396486122</v>
       </c>
       <c r="H42" t="n">
-        <v>202.1501815260438</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>84.49761230644286</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3859,10 +3859,10 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>30.62552924142298</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>221.4364741864697</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -3874,16 +3874,16 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>285.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>303.3731429098285</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>290.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>270.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3947,16 +3947,16 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>80.64702552265116</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>70.17031021621619</v>
       </c>
       <c r="W43" t="n">
-        <v>17.34155882655434</v>
+        <v>27.81827413298931</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
@@ -3975,10 +3975,10 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>402.4745782429939</v>
+        <v>340.9593118500768</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>362.3391557398498</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>355.5603873623931</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -4020,28 +4020,28 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>162.3297150939542</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>443.3593738324736</v>
+        <v>442.3593738324736</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>601.2055377546408</v>
       </c>
       <c r="V44" t="n">
-        <v>582.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>591.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>544.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>464.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4054,7 +4054,7 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>314.0999124455193</v>
+        <v>313.0999124455193</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -4063,16 +4063,16 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>292.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>278.6341396486122</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>283.1501815260438</v>
       </c>
       <c r="I45" t="n">
-        <v>166.4976123064429</v>
+        <v>165.4976123064429</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>111.625529241423</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -4105,10 +4105,10 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>357.9329444627969</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>323.6278570613623</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -4117,10 +4117,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>133.2103303720928</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>351.3913927661343</v>
       </c>
     </row>
     <row r="46">
@@ -4151,7 +4151,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>18.6004843492055</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>17.62038434920549</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4297,19 +4297,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1094.300429172222</v>
+        <v>297.8323074627289</v>
       </c>
       <c r="C2" t="n">
-        <v>1044.326107714653</v>
+        <v>247.8579860051593</v>
       </c>
       <c r="D2" t="n">
-        <v>1033.882516058239</v>
+        <v>237.4143943487453</v>
       </c>
       <c r="E2" t="n">
-        <v>625.4347487785736</v>
+        <v>221.3943447381695</v>
       </c>
       <c r="F2" t="n">
-        <v>620.495729881592</v>
+        <v>216.4553258411879</v>
       </c>
       <c r="G2" t="n">
         <v>212.8589749700837</v>
@@ -4321,22 +4321,22 @@
         <v>62.88</v>
       </c>
       <c r="J2" t="n">
-        <v>470.7407737914245</v>
+        <v>62.88</v>
       </c>
       <c r="K2" t="n">
-        <v>1205.253789033765</v>
+        <v>796.507210735987</v>
       </c>
       <c r="L2" t="n">
-        <v>1467.724888742899</v>
+        <v>824.6610055324326</v>
       </c>
       <c r="M2" t="n">
-        <v>2008.564901346513</v>
+        <v>1369.752775115639</v>
       </c>
       <c r="N2" t="n">
-        <v>2656.582248558462</v>
+        <v>2017.770122327588</v>
       </c>
       <c r="O2" t="n">
-        <v>2656.582248558462</v>
+        <v>1980.337671968498</v>
       </c>
       <c r="P2" t="n">
         <v>2684.341470726227</v>
@@ -4345,28 +4345,28 @@
         <v>3144</v>
       </c>
       <c r="R2" t="n">
-        <v>3144</v>
+        <v>2903.086116609154</v>
       </c>
       <c r="S2" t="n">
-        <v>2648.687501179319</v>
+        <v>2811.814021828878</v>
       </c>
       <c r="T2" t="n">
-        <v>2460.997319137879</v>
+        <v>2624.123839787437</v>
       </c>
       <c r="U2" t="n">
-        <v>2209.274553729151</v>
+        <v>2372.401074378709</v>
       </c>
       <c r="V2" t="n">
-        <v>1977.10180204549</v>
+        <v>2140.228322695049</v>
       </c>
       <c r="W2" t="n">
-        <v>1736.320513175846</v>
+        <v>1899.447033825405</v>
       </c>
       <c r="X2" t="n">
-        <v>1289.569869210991</v>
+        <v>1301.182555582306</v>
       </c>
       <c r="Y2" t="n">
-        <v>1177.128018016237</v>
+        <v>784.7003003471476</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>427.6273863086054</v>
+        <v>520.7033918272534</v>
       </c>
       <c r="C3" t="n">
-        <v>62.88</v>
+        <v>520.7033918272534</v>
       </c>
       <c r="D3" t="n">
-        <v>62.88</v>
+        <v>520.7033918272534</v>
       </c>
       <c r="E3" t="n">
-        <v>62.88</v>
+        <v>520.7033918272534</v>
       </c>
       <c r="F3" t="n">
-        <v>62.88</v>
+        <v>520.7033918272534</v>
       </c>
       <c r="G3" t="n">
-        <v>62.88</v>
+        <v>278.5341538448918</v>
       </c>
       <c r="H3" t="n">
-        <v>62.88</v>
+        <v>278.5341538448918</v>
       </c>
       <c r="I3" t="n">
         <v>62.88</v>
@@ -4433,19 +4433,19 @@
         <v>992.3700335895352</v>
       </c>
       <c r="U3" t="n">
-        <v>899.0885474669248</v>
+        <v>588.1241489451688</v>
       </c>
       <c r="V3" t="n">
-        <v>884.4313078795307</v>
+        <v>573.4669093577747</v>
       </c>
       <c r="W3" t="n">
-        <v>851.7311635261685</v>
+        <v>540.7667650044126</v>
       </c>
       <c r="X3" t="n">
-        <v>427.6273863086054</v>
+        <v>520.7033918272534</v>
       </c>
       <c r="Y3" t="n">
-        <v>427.6273863086054</v>
+        <v>520.7033918272534</v>
       </c>
     </row>
     <row r="4">
@@ -4455,28 +4455,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>791.5575759383521</v>
+        <v>734.8071443364649</v>
       </c>
       <c r="C4" t="n">
-        <v>917.5595817567879</v>
+        <v>860.8091501549007</v>
       </c>
       <c r="D4" t="n">
-        <v>1030.878725881788</v>
+        <v>860.8091501549007</v>
       </c>
       <c r="E4" t="n">
-        <v>1030.878725881788</v>
+        <v>860.8091501549007</v>
       </c>
       <c r="F4" t="n">
-        <v>1030.878725881788</v>
+        <v>860.8091501549007</v>
       </c>
       <c r="G4" t="n">
-        <v>1184.372768817854</v>
+        <v>860.8091501549007</v>
       </c>
       <c r="H4" t="n">
-        <v>1354.667104469054</v>
+        <v>1031.103485806102</v>
       </c>
       <c r="I4" t="n">
-        <v>1354.667104469054</v>
+        <v>1254.867038184807</v>
       </c>
       <c r="J4" t="n">
         <v>1377.343851994733</v>
@@ -4506,25 +4506,25 @@
         <v>62.88</v>
       </c>
       <c r="S4" t="n">
-        <v>62.88</v>
+        <v>101.6547414876158</v>
       </c>
       <c r="T4" t="n">
-        <v>62.88</v>
+        <v>101.6547414876158</v>
       </c>
       <c r="U4" t="n">
-        <v>309.4359641136965</v>
+        <v>101.6547414876158</v>
       </c>
       <c r="V4" t="n">
-        <v>508.2573569996424</v>
+        <v>300.4761343735617</v>
       </c>
       <c r="W4" t="n">
-        <v>680.1482752593198</v>
+        <v>472.3670526332392</v>
       </c>
       <c r="X4" t="n">
-        <v>680.1482752593198</v>
+        <v>623.3978436574326</v>
       </c>
       <c r="Y4" t="n">
-        <v>791.5575759383521</v>
+        <v>734.8071443364649</v>
       </c>
     </row>
     <row r="5">
@@ -4534,46 +4534,46 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>950.3742691963114</v>
+        <v>1498.340833212626</v>
       </c>
       <c r="C5" t="n">
-        <v>900.3999477387417</v>
+        <v>1448.366511755057</v>
       </c>
       <c r="D5" t="n">
-        <v>485.9159520419238</v>
+        <v>1437.922920098643</v>
       </c>
       <c r="E5" t="n">
-        <v>77.46818476225847</v>
+        <v>1029.475152818978</v>
       </c>
       <c r="F5" t="n">
-        <v>72.52916586527679</v>
+        <v>620.495729881592</v>
       </c>
       <c r="G5" t="n">
-        <v>68.93281499417266</v>
+        <v>212.8589749700837</v>
       </c>
       <c r="H5" t="n">
-        <v>62.88</v>
+        <v>206.8061599759111</v>
       </c>
       <c r="I5" t="n">
         <v>62.88</v>
       </c>
       <c r="J5" t="n">
-        <v>62.88</v>
+        <v>470.7407737914245</v>
       </c>
       <c r="K5" t="n">
-        <v>796.507210735987</v>
+        <v>1011.853388909256</v>
       </c>
       <c r="L5" t="n">
-        <v>1405.50387037222</v>
+        <v>1042.628230416794</v>
       </c>
       <c r="M5" t="n">
-        <v>1405.50387037222</v>
+        <v>1587.72</v>
       </c>
       <c r="N5" t="n">
-        <v>2053.521217584169</v>
+        <v>1587.72</v>
       </c>
       <c r="O5" t="n">
-        <v>2831.661217584169</v>
+        <v>2365.86</v>
       </c>
       <c r="P5" t="n">
         <v>3144</v>
@@ -4585,25 +4585,25 @@
         <v>2903.086116609154</v>
       </c>
       <c r="S5" t="n">
-        <v>2811.814021828878</v>
+        <v>2800.201335457563</v>
       </c>
       <c r="T5" t="n">
-        <v>2220.083435747033</v>
+        <v>2612.511153416122</v>
       </c>
       <c r="U5" t="n">
-        <v>1968.360670338305</v>
+        <v>2360.788388007394</v>
       </c>
       <c r="V5" t="n">
-        <v>1736.187918654644</v>
+        <v>2128.615636323734</v>
       </c>
       <c r="W5" t="n">
-        <v>1495.406629785</v>
+        <v>1887.83434745409</v>
       </c>
       <c r="X5" t="n">
-        <v>1301.182555582306</v>
+        <v>1693.610273251395</v>
       </c>
       <c r="Y5" t="n">
-        <v>1188.740704387552</v>
+        <v>1581.168422056641</v>
       </c>
     </row>
     <row r="6">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>62.88</v>
+        <v>681.9413001519231</v>
       </c>
       <c r="C6" t="n">
-        <v>62.88</v>
+        <v>317.1939138433177</v>
       </c>
       <c r="D6" t="n">
         <v>62.88</v>
@@ -4664,13 +4664,13 @@
         <v>1223.849614387097</v>
       </c>
       <c r="S6" t="n">
-        <v>1158.590714098848</v>
+        <v>754.550310058444</v>
       </c>
       <c r="T6" t="n">
-        <v>1153.607941914205</v>
+        <v>749.5675378738007</v>
       </c>
       <c r="U6" t="n">
-        <v>1153.402461310243</v>
+        <v>749.3620572698385</v>
       </c>
       <c r="V6" t="n">
         <v>734.7048176824444</v>
@@ -4679,10 +4679,10 @@
         <v>702.0046733290823</v>
       </c>
       <c r="X6" t="n">
-        <v>451.3209663094208</v>
+        <v>681.9413001519231</v>
       </c>
       <c r="Y6" t="n">
-        <v>451.3209663094208</v>
+        <v>681.9413001519231</v>
       </c>
     </row>
     <row r="7">
@@ -4692,28 +4692,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>781.5336647722413</v>
+        <v>1010.075483965232</v>
       </c>
       <c r="C7" t="n">
-        <v>781.5336647722413</v>
+        <v>1010.075483965232</v>
       </c>
       <c r="D7" t="n">
-        <v>781.5336647722413</v>
+        <v>1010.075483965232</v>
       </c>
       <c r="E7" t="n">
-        <v>781.5336647722413</v>
+        <v>1010.075483965232</v>
       </c>
       <c r="F7" t="n">
-        <v>829.7919210287604</v>
+        <v>1010.075483965232</v>
       </c>
       <c r="G7" t="n">
-        <v>983.285963964826</v>
+        <v>1010.075483965232</v>
       </c>
       <c r="H7" t="n">
-        <v>1153.580299616027</v>
+        <v>1010.075483965232</v>
       </c>
       <c r="I7" t="n">
-        <v>1377.343851994733</v>
+        <v>1010.075483965232</v>
       </c>
       <c r="J7" t="n">
         <v>1377.343851994733</v>
@@ -4749,19 +4749,19 @@
         <v>251.3294447325754</v>
       </c>
       <c r="U7" t="n">
-        <v>497.8854088462718</v>
+        <v>376.9230811163831</v>
       </c>
       <c r="V7" t="n">
-        <v>497.8854088462718</v>
+        <v>575.7444740023291</v>
       </c>
       <c r="W7" t="n">
-        <v>669.7763271059492</v>
+        <v>747.6353922620065</v>
       </c>
       <c r="X7" t="n">
-        <v>669.7763271059492</v>
+        <v>898.6661832862</v>
       </c>
       <c r="Y7" t="n">
-        <v>669.7763271059492</v>
+        <v>1010.075483965232</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1346.826998934383</v>
+        <v>1105.913115543537</v>
       </c>
       <c r="C8" t="n">
-        <v>892.8122734364093</v>
+        <v>651.8983900455634</v>
       </c>
       <c r="D8" t="n">
-        <v>882.3686817799954</v>
+        <v>641.4547983891495</v>
       </c>
       <c r="E8" t="n">
-        <v>473.9209145003301</v>
+        <v>637.0474351498882</v>
       </c>
       <c r="F8" t="n">
-        <v>216.4553258411879</v>
+        <v>620.495729881592</v>
       </c>
       <c r="G8" t="n">
-        <v>212.8589749700837</v>
+        <v>616.8993790104878</v>
       </c>
       <c r="H8" t="n">
         <v>206.8061599759111</v>
@@ -4798,16 +4798,16 @@
         <v>62.88</v>
       </c>
       <c r="K8" t="n">
-        <v>797.3930152423408</v>
+        <v>796.507210735987</v>
       </c>
       <c r="L8" t="n">
-        <v>823.9160997702853</v>
+        <v>1502.082592939338</v>
       </c>
       <c r="M8" t="n">
-        <v>1369.007869353492</v>
+        <v>2047.174362522544</v>
       </c>
       <c r="N8" t="n">
-        <v>1878.442248558462</v>
+        <v>2695.191709734493</v>
       </c>
       <c r="O8" t="n">
         <v>2656.582248558462</v>
@@ -4819,28 +4819,28 @@
         <v>3144</v>
       </c>
       <c r="R8" t="n">
-        <v>3144</v>
+        <v>2903.086116609154</v>
       </c>
       <c r="S8" t="n">
-        <v>2648.687501179319</v>
+        <v>2811.814021828878</v>
       </c>
       <c r="T8" t="n">
-        <v>2460.997319137879</v>
+        <v>2624.123839787437</v>
       </c>
       <c r="U8" t="n">
-        <v>2209.274553729151</v>
+        <v>2372.401074378709</v>
       </c>
       <c r="V8" t="n">
-        <v>1977.10180204549</v>
+        <v>2140.228322695049</v>
       </c>
       <c r="W8" t="n">
-        <v>1736.320513175846</v>
+        <v>1495.406629785</v>
       </c>
       <c r="X8" t="n">
-        <v>1542.096438973152</v>
+        <v>1301.182555582306</v>
       </c>
       <c r="Y8" t="n">
-        <v>1429.654587778398</v>
+        <v>1188.740704387552</v>
       </c>
     </row>
     <row r="9">
@@ -4856,19 +4856,19 @@
         <v>681.9413001519232</v>
       </c>
       <c r="D9" t="n">
-        <v>330.4890911643448</v>
+        <v>681.9413001519232</v>
       </c>
       <c r="E9" t="n">
-        <v>330.4890911643448</v>
+        <v>391.8033733824366</v>
       </c>
       <c r="F9" t="n">
-        <v>278.5341538448918</v>
+        <v>391.8033733824366</v>
       </c>
       <c r="G9" t="n">
-        <v>278.5341538448918</v>
+        <v>62.88</v>
       </c>
       <c r="H9" t="n">
-        <v>278.5341538448918</v>
+        <v>62.88</v>
       </c>
       <c r="I9" t="n">
         <v>62.88</v>
@@ -4898,10 +4898,10 @@
         <v>1366.001115368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1223.849614387097</v>
+        <v>819.8092103466926</v>
       </c>
       <c r="S9" t="n">
-        <v>1158.590714098848</v>
+        <v>754.5503100584441</v>
       </c>
       <c r="T9" t="n">
         <v>749.5675378738008</v>
@@ -4929,31 +4929,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>981.3631084501613</v>
+        <v>980.695363083115</v>
       </c>
       <c r="C10" t="n">
-        <v>1107.365114268597</v>
+        <v>1106.697368901551</v>
       </c>
       <c r="D10" t="n">
-        <v>1220.684258393597</v>
+        <v>1220.016513026551</v>
       </c>
       <c r="E10" t="n">
-        <v>1220.684258393597</v>
+        <v>1220.016513026551</v>
       </c>
       <c r="F10" t="n">
-        <v>1220.684258393597</v>
+        <v>1344.377485618486</v>
       </c>
       <c r="G10" t="n">
-        <v>1220.684258393597</v>
+        <v>1497.871528554552</v>
       </c>
       <c r="H10" t="n">
-        <v>1377.343851994733</v>
+        <v>1497.871528554552</v>
       </c>
       <c r="I10" t="n">
-        <v>1377.343851994733</v>
+        <v>1497.871528554552</v>
       </c>
       <c r="J10" t="n">
-        <v>1377.343851994733</v>
+        <v>1497.871528554552</v>
       </c>
       <c r="K10" t="n">
         <v>1497.871528554552</v>
@@ -4983,22 +4983,22 @@
         <v>101.6547414876158</v>
       </c>
       <c r="T10" t="n">
-        <v>101.6547414876158</v>
+        <v>290.1041862201911</v>
       </c>
       <c r="U10" t="n">
-        <v>348.2107056013122</v>
+        <v>290.1041862201911</v>
       </c>
       <c r="V10" t="n">
-        <v>547.0320984872582</v>
+        <v>488.925579106137</v>
       </c>
       <c r="W10" t="n">
-        <v>718.9230167469356</v>
+        <v>660.8164973658145</v>
       </c>
       <c r="X10" t="n">
-        <v>869.953807771129</v>
+        <v>811.847288390008</v>
       </c>
       <c r="Y10" t="n">
-        <v>981.3631084501613</v>
+        <v>923.2565890690403</v>
       </c>
     </row>
     <row r="11">
@@ -5008,19 +5008,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1251.384370206413</v>
+        <v>1066.001369296374</v>
       </c>
       <c r="C11" t="n">
-        <v>1016.561563900358</v>
+        <v>831.1785629903193</v>
       </c>
       <c r="D11" t="n">
-        <v>821.2694873954592</v>
+        <v>635.8864864854205</v>
       </c>
       <c r="E11" t="n">
-        <v>632.0136393077131</v>
+        <v>446.6306383976744</v>
       </c>
       <c r="F11" t="n">
-        <v>442.2261355622466</v>
+        <v>256.8431346522078</v>
       </c>
       <c r="G11" t="n">
         <v>253.7812998426575</v>
@@ -5032,25 +5032,25 @@
         <v>62.88</v>
       </c>
       <c r="J11" t="n">
-        <v>62.88</v>
+        <v>308.1152151744532</v>
       </c>
       <c r="K11" t="n">
-        <v>87.68664889447237</v>
+        <v>1042.628230416794</v>
       </c>
       <c r="L11" t="n">
-        <v>865.8266488944723</v>
+        <v>1820.768230416794</v>
       </c>
       <c r="M11" t="n">
-        <v>865.8266488944723</v>
+        <v>2365.86</v>
       </c>
       <c r="N11" t="n">
-        <v>1128.061470726228</v>
+        <v>2365.86</v>
       </c>
       <c r="O11" t="n">
-        <v>1906.201470726227</v>
+        <v>2365.86</v>
       </c>
       <c r="P11" t="n">
-        <v>2684.341470726227</v>
+        <v>3144</v>
       </c>
       <c r="Q11" t="n">
         <v>3144</v>
@@ -5062,22 +5062,22 @@
         <v>2846.157456172312</v>
       </c>
       <c r="T11" t="n">
-        <v>2846.157456172312</v>
+        <v>2473.618789282386</v>
       </c>
       <c r="U11" t="n">
-        <v>2409.586205915099</v>
+        <v>2473.618789282386</v>
       </c>
       <c r="V11" t="n">
-        <v>2323.76277666822</v>
+        <v>2056.597552750241</v>
       </c>
       <c r="W11" t="n">
-        <v>1898.133002950092</v>
+        <v>1630.967779032112</v>
       </c>
       <c r="X11" t="n">
-        <v>1519.060443898912</v>
+        <v>1630.967779032112</v>
       </c>
       <c r="Y11" t="n">
-        <v>1519.060443898912</v>
+        <v>1333.677442988873</v>
       </c>
     </row>
     <row r="12">
@@ -5123,10 +5123,10 @@
         <v>1672.048239556439</v>
       </c>
       <c r="N12" t="n">
-        <v>2047.296208031931</v>
+        <v>1861.20551446707</v>
       </c>
       <c r="O12" t="n">
-        <v>2525.994338677915</v>
+        <v>2339.903645113053</v>
       </c>
       <c r="P12" t="n">
         <v>2687.187785620296</v>
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>951.8284233757123</v>
+        <v>1124.111642933685</v>
       </c>
       <c r="C14" t="n">
-        <v>739.2278392918801</v>
+        <v>910.5009578397519</v>
       </c>
       <c r="D14" t="n">
-        <v>566.1579850092035</v>
+        <v>736.4210025469743</v>
       </c>
       <c r="E14" t="n">
-        <v>399.1243591436796</v>
+        <v>568.3772756713494</v>
       </c>
       <c r="F14" t="n">
-        <v>231.5590776204353</v>
+        <v>399.8018931380041</v>
       </c>
       <c r="G14" t="n">
-        <v>231.5590776204353</v>
+        <v>232.5691786305363</v>
       </c>
       <c r="H14" t="n">
         <v>62.88</v>
@@ -5272,16 +5272,16 @@
         <v>470.7407737914245</v>
       </c>
       <c r="K14" t="n">
-        <v>1205.253789033765</v>
+        <v>495.5474226858968</v>
       </c>
       <c r="L14" t="n">
-        <v>1793.009008249028</v>
+        <v>1273.687422685897</v>
       </c>
       <c r="M14" t="n">
-        <v>2338.100777832235</v>
+        <v>1818.779192269104</v>
       </c>
       <c r="N14" t="n">
-        <v>2338.100777832235</v>
+        <v>2466.796539481053</v>
       </c>
       <c r="O14" t="n">
         <v>3116.240777832234</v>
@@ -5293,28 +5293,28 @@
         <v>3144</v>
       </c>
       <c r="R14" t="n">
-        <v>3144</v>
+        <v>3143.490157013194</v>
       </c>
       <c r="S14" t="n">
-        <v>3144</v>
+        <v>2888.581698596554</v>
       </c>
       <c r="T14" t="n">
-        <v>2793.683555332297</v>
+        <v>2537.255152918749</v>
       </c>
       <c r="U14" t="n">
-        <v>2379.334527297306</v>
+        <v>2121.896023873658</v>
       </c>
       <c r="V14" t="n">
-        <v>1984.535512987383</v>
+        <v>2004.514248084239</v>
       </c>
       <c r="W14" t="n">
-        <v>1581.127961491476</v>
+        <v>2004.514248084239</v>
       </c>
       <c r="X14" t="n">
-        <v>1224.277624662519</v>
+        <v>1646.653810245181</v>
       </c>
       <c r="Y14" t="n">
-        <v>1197.28227484599</v>
+        <v>1370.575595414063</v>
       </c>
     </row>
     <row r="15">
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>683.213596038048</v>
+        <v>689.2742020986541</v>
       </c>
       <c r="C15" t="n">
-        <v>559.880351143584</v>
+        <v>564.9308561940891</v>
       </c>
       <c r="D15" t="n">
-        <v>449.842283570147</v>
+        <v>453.882687610551</v>
       </c>
       <c r="E15" t="n">
-        <v>345.122993447003</v>
+        <v>348.153296477306</v>
       </c>
       <c r="F15" t="n">
-        <v>243.4702234087435</v>
+        <v>245.4904254289455</v>
       </c>
       <c r="G15" t="n">
-        <v>155.9609914404483</v>
+        <v>156.9710924505493</v>
       </c>
       <c r="H15" t="n">
         <v>62.88</v>
       </c>
       <c r="I15" t="n">
-        <v>62.88</v>
+        <v>87.13736381662156</v>
       </c>
       <c r="J15" t="n">
-        <v>433.3045759300159</v>
+        <v>220.9519397466375</v>
       </c>
       <c r="K15" t="n">
-        <v>875.9563794772296</v>
+        <v>662.6137432938511</v>
       </c>
       <c r="L15" t="n">
-        <v>1406.572383996958</v>
+        <v>1192.239747813579</v>
       </c>
       <c r="M15" t="n">
-        <v>1519.090875739817</v>
+        <v>1304.758239556439</v>
       </c>
       <c r="N15" t="n">
-        <v>1777.722907184729</v>
+        <v>1480.653696285253</v>
       </c>
       <c r="O15" t="n">
-        <v>2041.591037830712</v>
+        <v>1980.141826931236</v>
       </c>
       <c r="P15" t="n">
-        <v>2410.655178337954</v>
+        <v>2348.215967438478</v>
       </c>
       <c r="Q15" t="n">
-        <v>2410.655178337954</v>
+        <v>2425.80669348947</v>
       </c>
       <c r="R15" t="n">
-        <v>2105.877414730252</v>
+        <v>2120.018828871667</v>
       </c>
       <c r="S15" t="n">
-        <v>1877.992251815741</v>
+        <v>1891.123564947055</v>
       </c>
       <c r="T15" t="n">
-        <v>1710.383217004836</v>
+        <v>1722.504429126048</v>
       </c>
       <c r="U15" t="n">
-        <v>1547.551473774611</v>
+        <v>1558.662584885722</v>
       </c>
       <c r="V15" t="n">
-        <v>1370.267971560954</v>
+        <v>1380.368981661964</v>
       </c>
       <c r="W15" t="n">
-        <v>1174.941564581329</v>
+        <v>1184.032473672238</v>
       </c>
       <c r="X15" t="n">
-        <v>992.2519287779076</v>
+        <v>1000.332736858716</v>
       </c>
       <c r="Y15" t="n">
-        <v>830.2404209333274</v>
+        <v>837.3111280040346</v>
       </c>
     </row>
     <row r="16">
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>173.553883345865</v>
+        <v>217.5386842039078</v>
       </c>
       <c r="C16" t="n">
-        <v>139.4879776407693</v>
+        <v>182.4626774887112</v>
       </c>
       <c r="D16" t="n">
-        <v>139.4879776407693</v>
+        <v>182.4626774887112</v>
       </c>
       <c r="E16" t="n">
-        <v>97.08302326000512</v>
+        <v>182.4626774887112</v>
       </c>
       <c r="F16" t="n">
-        <v>97.08302326000512</v>
+        <v>182.4626774887112</v>
       </c>
       <c r="G16" t="n">
-        <v>97.08302326000512</v>
+        <v>182.4626774887112</v>
       </c>
       <c r="H16" t="n">
-        <v>107.987358911206</v>
+        <v>192.377013139912</v>
       </c>
       <c r="I16" t="n">
-        <v>172.3609112899118</v>
+        <v>255.7605655186179</v>
       </c>
       <c r="J16" t="n">
-        <v>380.2392793194123</v>
+        <v>462.6489335481184</v>
       </c>
       <c r="K16" t="n">
-        <v>380.2392793194123</v>
+        <v>462.6489335481184</v>
       </c>
       <c r="L16" t="n">
-        <v>380.2392793194123</v>
+        <v>462.6489335481184</v>
       </c>
       <c r="M16" t="n">
-        <v>380.2392793194123</v>
+        <v>462.6489335481184</v>
       </c>
       <c r="N16" t="n">
-        <v>380.2392793194123</v>
+        <v>462.6489335481184</v>
       </c>
       <c r="O16" t="n">
-        <v>380.2392793194123</v>
+        <v>462.6489335481184</v>
       </c>
       <c r="P16" t="n">
-        <v>185.9442368252058</v>
+        <v>462.6489335481184</v>
       </c>
       <c r="Q16" t="n">
-        <v>185.9442368252058</v>
+        <v>62.88</v>
       </c>
       <c r="R16" t="n">
-        <v>185.9442368252058</v>
+        <v>62.88</v>
       </c>
       <c r="S16" t="n">
         <v>62.88</v>
       </c>
       <c r="T16" t="n">
-        <v>91.93944473257535</v>
+        <v>90.94944473257536</v>
       </c>
       <c r="U16" t="n">
-        <v>179.1054088462718</v>
+        <v>177.1254088462719</v>
       </c>
       <c r="V16" t="n">
-        <v>218.5368017322178</v>
+        <v>215.5668017322178</v>
       </c>
       <c r="W16" t="n">
-        <v>231.0377199918952</v>
+        <v>227.0777199918952</v>
       </c>
       <c r="X16" t="n">
-        <v>222.5087852140088</v>
+        <v>217.5386842039078</v>
       </c>
       <c r="Y16" t="n">
-        <v>173.553883345865</v>
+        <v>217.5386842039078</v>
       </c>
     </row>
     <row r="17">
@@ -5512,19 +5512,19 @@
         <v>797.3930152423408</v>
       </c>
       <c r="L17" t="n">
-        <v>1575.533015242341</v>
+        <v>1463.473131763306</v>
       </c>
       <c r="M17" t="n">
-        <v>2120.624784825547</v>
+        <v>2008.564901346513</v>
       </c>
       <c r="N17" t="n">
-        <v>2768.642132037496</v>
+        <v>2656.582248558462</v>
       </c>
       <c r="O17" t="n">
-        <v>3116.240777832234</v>
+        <v>2656.582248558462</v>
       </c>
       <c r="P17" t="n">
-        <v>3144</v>
+        <v>2684.341470726227</v>
       </c>
       <c r="Q17" t="n">
         <v>3144</v>
@@ -5533,13 +5533,13 @@
         <v>3144</v>
       </c>
       <c r="S17" t="n">
-        <v>2941.123660330137</v>
+        <v>2937.576390068209</v>
       </c>
       <c r="T17" t="n">
-        <v>2638.281963137181</v>
+        <v>2634.734692875253</v>
       </c>
       <c r="U17" t="n">
-        <v>2271.407682576938</v>
+        <v>2267.860412315009</v>
       </c>
       <c r="V17" t="n">
         <v>1924.083415741762</v>
@@ -5597,13 +5597,13 @@
         <v>809.2608757398173</v>
       </c>
       <c r="N18" t="n">
-        <v>1252.81884421531</v>
+        <v>969.6788442153101</v>
       </c>
       <c r="O18" t="n">
-        <v>1566.0798257095</v>
+        <v>1440.969099658508</v>
       </c>
       <c r="P18" t="n">
-        <v>1698.533966216742</v>
+        <v>1573.423240165751</v>
       </c>
       <c r="Q18" t="n">
         <v>1698.533966216742</v>
@@ -5640,55 +5640,55 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>454.2034601705548</v>
+        <v>455.3285110160888</v>
       </c>
       <c r="C19" t="n">
-        <v>467.3454659889906</v>
+        <v>468.4705168345246</v>
       </c>
       <c r="D19" t="n">
-        <v>467.8046101139906</v>
+        <v>468.9296609595247</v>
       </c>
       <c r="E19" t="n">
-        <v>472.7735143254037</v>
+        <v>473.8985651709377</v>
       </c>
       <c r="F19" t="n">
-        <v>484.2744869173391</v>
+        <v>485.3995377628731</v>
       </c>
       <c r="G19" t="n">
-        <v>524.9085298534047</v>
+        <v>526.0335806989387</v>
       </c>
       <c r="H19" t="n">
-        <v>582.3428655046056</v>
+        <v>583.4679163501396</v>
       </c>
       <c r="I19" t="n">
-        <v>693.2464178833114</v>
+        <v>694.3714687288455</v>
       </c>
       <c r="J19" t="n">
-        <v>947.654785912812</v>
+        <v>948.7798367583459</v>
       </c>
       <c r="K19" t="n">
-        <v>955.3224624726313</v>
+        <v>956.4475133181652</v>
       </c>
       <c r="L19" t="n">
-        <v>829.6549791537949</v>
+        <v>830.7800299993288</v>
       </c>
       <c r="M19" t="n">
-        <v>606.6441943292289</v>
+        <v>830.7800299993288</v>
       </c>
       <c r="N19" t="n">
-        <v>606.6441943292289</v>
+        <v>556.3724692844294</v>
       </c>
       <c r="O19" t="n">
-        <v>606.6441943292289</v>
+        <v>533.1776485990911</v>
       </c>
       <c r="P19" t="n">
-        <v>499.6883499248465</v>
+        <v>138.4694893504584</v>
       </c>
       <c r="Q19" t="n">
-        <v>62.88</v>
+        <v>138.4694893504584</v>
       </c>
       <c r="R19" t="n">
-        <v>62.88</v>
+        <v>138.4694893504584</v>
       </c>
       <c r="S19" t="n">
         <v>62.88</v>
@@ -5743,25 +5743,25 @@
         <v>62.96</v>
       </c>
       <c r="J20" t="n">
-        <v>470.8207737914245</v>
+        <v>62.96</v>
       </c>
       <c r="K20" t="n">
-        <v>1205.333789033765</v>
+        <v>797.4730152423408</v>
       </c>
       <c r="L20" t="n">
-        <v>1984.463789033765</v>
+        <v>1576.603015242341</v>
       </c>
       <c r="M20" t="n">
-        <v>1984.463789033765</v>
+        <v>1576.603015242341</v>
       </c>
       <c r="N20" t="n">
-        <v>2368.87</v>
+        <v>2224.62036245429</v>
       </c>
       <c r="O20" t="n">
-        <v>2368.87</v>
+        <v>2660.582248558462</v>
       </c>
       <c r="P20" t="n">
-        <v>3148</v>
+        <v>2688.341470726227</v>
       </c>
       <c r="Q20" t="n">
         <v>3148</v>
@@ -5822,25 +5822,25 @@
         <v>62.96</v>
       </c>
       <c r="J21" t="n">
-        <v>246.1674267782223</v>
+        <v>196.7745759300159</v>
       </c>
       <c r="K21" t="n">
-        <v>452.2092303254359</v>
+        <v>402.8163794772295</v>
       </c>
       <c r="L21" t="n">
-        <v>746.2152348451643</v>
+        <v>696.822383996958</v>
       </c>
       <c r="M21" t="n">
-        <v>858.7337265880235</v>
+        <v>809.3408757398172</v>
       </c>
       <c r="N21" t="n">
-        <v>1302.291695063516</v>
+        <v>1177.180969012525</v>
       </c>
       <c r="O21" t="n">
-        <v>1566.1598257095</v>
+        <v>1441.049099658508</v>
       </c>
       <c r="P21" t="n">
-        <v>1698.613966216742</v>
+        <v>1573.503240165751</v>
       </c>
       <c r="Q21" t="n">
         <v>1698.613966216742</v>
@@ -5877,55 +5877,55 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>454.2834601705548</v>
+        <v>452.8033057771585</v>
       </c>
       <c r="C22" t="n">
-        <v>467.4254659889906</v>
+        <v>465.9453115955943</v>
       </c>
       <c r="D22" t="n">
-        <v>467.8846101139907</v>
+        <v>466.4044557205943</v>
       </c>
       <c r="E22" t="n">
-        <v>472.8535143254037</v>
+        <v>471.3733599320074</v>
       </c>
       <c r="F22" t="n">
-        <v>484.3544869173392</v>
+        <v>482.8743325239428</v>
       </c>
       <c r="G22" t="n">
-        <v>524.9885298534048</v>
+        <v>523.5083754600084</v>
       </c>
       <c r="H22" t="n">
-        <v>582.4228655046056</v>
+        <v>580.9427111112093</v>
       </c>
       <c r="I22" t="n">
-        <v>693.3264178833115</v>
+        <v>691.8462634899151</v>
       </c>
       <c r="J22" t="n">
-        <v>947.734785912812</v>
+        <v>946.2546315194156</v>
       </c>
       <c r="K22" t="n">
-        <v>955.4024624726311</v>
+        <v>953.9223080792348</v>
       </c>
       <c r="L22" t="n">
-        <v>898.7076659028836</v>
+        <v>878.6679385282168</v>
       </c>
       <c r="M22" t="n">
-        <v>898.7076659028836</v>
+        <v>878.6679385282168</v>
       </c>
       <c r="N22" t="n">
-        <v>898.7076659028836</v>
+        <v>878.6679385282168</v>
       </c>
       <c r="O22" t="n">
-        <v>898.7076659028836</v>
+        <v>533.257648599091</v>
       </c>
       <c r="P22" t="n">
-        <v>503.9995066542509</v>
+        <v>138.5494893504584</v>
       </c>
       <c r="Q22" t="n">
-        <v>503.9995066542509</v>
+        <v>138.5494893504584</v>
       </c>
       <c r="R22" t="n">
-        <v>62.96</v>
+        <v>138.5494893504584</v>
       </c>
       <c r="S22" t="n">
         <v>62.96</v>
@@ -5946,7 +5946,7 @@
         <v>455.4085110160888</v>
       </c>
       <c r="Y22" t="n">
-        <v>455.4085110160888</v>
+        <v>453.9283566226925</v>
       </c>
     </row>
     <row r="23">
@@ -5980,25 +5980,25 @@
         <v>62.96</v>
       </c>
       <c r="J23" t="n">
-        <v>62.96</v>
+        <v>470.8207737914245</v>
       </c>
       <c r="K23" t="n">
-        <v>87.76664889447235</v>
+        <v>1205.333789033765</v>
       </c>
       <c r="L23" t="n">
-        <v>396.6308832048414</v>
+        <v>1467.473131763306</v>
       </c>
       <c r="M23" t="n">
-        <v>941.7226527880479</v>
+        <v>2012.564901346513</v>
       </c>
       <c r="N23" t="n">
-        <v>1589.739999999997</v>
+        <v>2660.582248558462</v>
       </c>
       <c r="O23" t="n">
-        <v>2368.869999999999</v>
+        <v>2660.582248558462</v>
       </c>
       <c r="P23" t="n">
-        <v>3148</v>
+        <v>2688.341470726227</v>
       </c>
       <c r="Q23" t="n">
         <v>3148</v>
@@ -6071,10 +6071,10 @@
         <v>809.3408757398172</v>
       </c>
       <c r="N24" t="n">
-        <v>1252.89884421531</v>
+        <v>1019.151695063516</v>
       </c>
       <c r="O24" t="n">
-        <v>1516.766974861293</v>
+        <v>1283.019825709499</v>
       </c>
       <c r="P24" t="n">
         <v>1698.613966216742</v>
@@ -6114,55 +6114,55 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>454.2834601705548</v>
+        <v>455.4085110160888</v>
       </c>
       <c r="C25" t="n">
-        <v>467.4254659889906</v>
+        <v>468.5505168345246</v>
       </c>
       <c r="D25" t="n">
-        <v>467.8846101139907</v>
+        <v>469.0096609595247</v>
       </c>
       <c r="E25" t="n">
-        <v>472.8535143254037</v>
+        <v>473.9785651709377</v>
       </c>
       <c r="F25" t="n">
-        <v>484.3544869173392</v>
+        <v>485.4795377628732</v>
       </c>
       <c r="G25" t="n">
-        <v>524.9885298534048</v>
+        <v>526.1135806989388</v>
       </c>
       <c r="H25" t="n">
-        <v>582.4228655046056</v>
+        <v>583.5479163501396</v>
       </c>
       <c r="I25" t="n">
-        <v>693.3264178833115</v>
+        <v>694.4514687288455</v>
       </c>
       <c r="J25" t="n">
-        <v>947.734785912812</v>
+        <v>948.8598367583461</v>
       </c>
       <c r="K25" t="n">
-        <v>955.4024624726311</v>
+        <v>956.5275133181652</v>
       </c>
       <c r="L25" t="n">
-        <v>955.4024624726311</v>
+        <v>956.5275133181652</v>
       </c>
       <c r="M25" t="n">
-        <v>955.4024624726311</v>
+        <v>956.5275133181652</v>
       </c>
       <c r="N25" t="n">
-        <v>955.4024624726311</v>
+        <v>956.5275133181652</v>
       </c>
       <c r="O25" t="n">
-        <v>955.4024624726311</v>
+        <v>611.1172233890393</v>
       </c>
       <c r="P25" t="n">
-        <v>955.4024624726311</v>
+        <v>216.4090641404066</v>
       </c>
       <c r="Q25" t="n">
-        <v>579.5889960047093</v>
+        <v>62.96</v>
       </c>
       <c r="R25" t="n">
-        <v>138.5494893504584</v>
+        <v>62.96</v>
       </c>
       <c r="S25" t="n">
         <v>62.96</v>
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>622.1281875528017</v>
+        <v>923.5880567639861</v>
       </c>
       <c r="C26" t="n">
-        <v>622.1281875528017</v>
+        <v>688.7652504579316</v>
       </c>
       <c r="D26" t="n">
-        <v>622.1281875528017</v>
+        <v>493.4731739530329</v>
       </c>
       <c r="E26" t="n">
-        <v>432.8723394650556</v>
+        <v>433.9861355622486</v>
       </c>
       <c r="F26" t="n">
-        <v>243.084835719589</v>
+        <v>433.9861355622486</v>
       </c>
       <c r="G26" t="n">
-        <v>54.64</v>
+        <v>245.5412998426596</v>
       </c>
       <c r="H26" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="I26" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="J26" t="n">
-        <v>54.64</v>
+        <v>462.5007737914266</v>
       </c>
       <c r="K26" t="n">
-        <v>730.8099999999999</v>
+        <v>1020.698290255874</v>
       </c>
       <c r="L26" t="n">
-        <v>1406.98</v>
+        <v>1051.473131763411</v>
       </c>
       <c r="M26" t="n">
-        <v>1952.071769583206</v>
+        <v>1596.564901346618</v>
       </c>
       <c r="N26" t="n">
-        <v>2028.070777832229</v>
+        <v>2244.582248558567</v>
       </c>
       <c r="O26" t="n">
-        <v>2704.240777832234</v>
+        <v>2244.582248558567</v>
       </c>
       <c r="P26" t="n">
-        <v>2732</v>
+        <v>2272.341470726332</v>
       </c>
       <c r="Q26" t="n">
-        <v>2732</v>
+        <v>2732.000000000105</v>
       </c>
       <c r="R26" t="n">
-        <v>2732</v>
+        <v>2710.278035801178</v>
       </c>
       <c r="S26" t="n">
-        <v>2455.879420371239</v>
+        <v>2710.278035801178</v>
       </c>
       <c r="T26" t="n">
-        <v>2083.340753481313</v>
+        <v>2710.278035801178</v>
       </c>
       <c r="U26" t="n">
-        <v>1646.7695032241</v>
+        <v>2710.278035801178</v>
       </c>
       <c r="V26" t="n">
-        <v>1229.748266691955</v>
+        <v>2293.256799269033</v>
       </c>
       <c r="W26" t="n">
-        <v>804.1184929738258</v>
+        <v>1867.627025550904</v>
       </c>
       <c r="X26" t="n">
-        <v>804.1184929738258</v>
+        <v>1488.554466499724</v>
       </c>
       <c r="Y26" t="n">
-        <v>622.1281875528017</v>
+        <v>1191.264130456486</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>804.5584177000937</v>
+        <v>808.3069293713834</v>
       </c>
       <c r="C27" t="n">
-        <v>659.0029505834076</v>
+        <v>662.7514622546972</v>
       </c>
       <c r="D27" t="n">
-        <v>526.7426607877484</v>
+        <v>530.491172459038</v>
       </c>
       <c r="E27" t="n">
-        <v>399.8011484423821</v>
+        <v>403.5496601136717</v>
       </c>
       <c r="F27" t="n">
-        <v>275.9261561819004</v>
+        <v>279.67466785319</v>
       </c>
       <c r="G27" t="n">
-        <v>169.9432136626705</v>
+        <v>169.9432136626726</v>
       </c>
       <c r="H27" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="I27" t="n">
-        <v>58.10736381662156</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="J27" t="n">
-        <v>406.7519397466375</v>
+        <v>403.284575930018</v>
       </c>
       <c r="K27" t="n">
-        <v>827.623743293851</v>
+        <v>824.1563794772317</v>
       </c>
       <c r="L27" t="n">
-        <v>1336.459747813579</v>
+        <v>1332.99238399696</v>
       </c>
       <c r="M27" t="n">
-        <v>1663.808239556439</v>
+        <v>1473.969034320395</v>
       </c>
       <c r="N27" t="n">
-        <v>2039.056208031932</v>
+        <v>1849.217002795888</v>
       </c>
       <c r="O27" t="n">
-        <v>2327.915133441766</v>
+        <v>2327.915133441871</v>
       </c>
       <c r="P27" t="n">
-        <v>2675.199273949009</v>
+        <v>2675.199273949114</v>
       </c>
       <c r="Q27" t="n">
-        <v>2732</v>
+        <v>2732.000000000105</v>
       </c>
       <c r="R27" t="n">
-        <v>2405.000014170076</v>
+        <v>2408.748525841366</v>
       </c>
       <c r="S27" t="n">
-        <v>2154.892629033343</v>
+        <v>2158.641140704633</v>
       </c>
       <c r="T27" t="n">
-        <v>1965.061372000215</v>
+        <v>1968.809883671505</v>
       </c>
       <c r="U27" t="n">
-        <v>1780.007406547768</v>
+        <v>1783.755918219058</v>
       </c>
       <c r="V27" t="n">
-        <v>1580.501682111889</v>
+        <v>1584.250193783178</v>
       </c>
       <c r="W27" t="n">
-        <v>1362.953052910042</v>
+        <v>1366.701564581331</v>
       </c>
       <c r="X27" t="n">
-        <v>1158.041194884398</v>
+        <v>1161.789706555687</v>
       </c>
       <c r="Y27" t="n">
-        <v>973.8074648175954</v>
+        <v>977.555976488885</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>65.7364843881228</v>
+        <v>144.9568017322199</v>
       </c>
       <c r="C28" t="n">
-        <v>65.7364843881228</v>
+        <v>144.9568017322199</v>
       </c>
       <c r="D28" t="n">
-        <v>65.7364843881228</v>
+        <v>144.9568017322199</v>
       </c>
       <c r="E28" t="n">
-        <v>65.7364843881228</v>
+        <v>144.9568017322199</v>
       </c>
       <c r="F28" t="n">
-        <v>65.7364843881228</v>
+        <v>144.9568017322199</v>
       </c>
       <c r="G28" t="n">
-        <v>65.7364843881228</v>
+        <v>144.9568017322199</v>
       </c>
       <c r="H28" t="n">
-        <v>54.64</v>
+        <v>133.8603173440971</v>
       </c>
       <c r="I28" t="n">
-        <v>97.23355237870587</v>
+        <v>176.4538697228029</v>
       </c>
       <c r="J28" t="n">
-        <v>283.3319204082064</v>
+        <v>362.5522377523034</v>
       </c>
       <c r="K28" t="n">
-        <v>283.3319204082064</v>
+        <v>362.5522377523034</v>
       </c>
       <c r="L28" t="n">
-        <v>283.3319204082064</v>
+        <v>362.5522377523034</v>
       </c>
       <c r="M28" t="n">
-        <v>283.3319204082064</v>
+        <v>362.5522377523034</v>
       </c>
       <c r="N28" t="n">
-        <v>283.3319204082064</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="O28" t="n">
-        <v>283.3319204082064</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="P28" t="n">
-        <v>283.3319204082064</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="Q28" t="n">
-        <v>56.06429143183637</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="R28" t="n">
-        <v>56.06429143183637</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="S28" t="n">
-        <v>56.06429143183637</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="T28" t="n">
-        <v>63.34373616441172</v>
+        <v>61.91944473257746</v>
       </c>
       <c r="U28" t="n">
-        <v>128.7297002781082</v>
+        <v>127.3054088462739</v>
       </c>
       <c r="V28" t="n">
-        <v>146.3810931640542</v>
+        <v>144.9568017322199</v>
       </c>
       <c r="W28" t="n">
-        <v>136.9136084784888</v>
+        <v>144.9568017322199</v>
       </c>
       <c r="X28" t="n">
-        <v>136.9136084784888</v>
+        <v>144.9568017322199</v>
       </c>
       <c r="Y28" t="n">
-        <v>65.7364843881228</v>
+        <v>144.9568017322199</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>663.3945074805117</v>
+        <v>879.5080065700508</v>
       </c>
       <c r="C29" t="n">
-        <v>489.1777617805179</v>
+        <v>705.2912608700569</v>
       </c>
       <c r="D29" t="n">
-        <v>441.4238018318108</v>
+        <v>570.6052449712188</v>
       </c>
       <c r="E29" t="n">
-        <v>312.7740143501253</v>
+        <v>441.9554574895333</v>
       </c>
       <c r="F29" t="n">
-        <v>312.7740143501253</v>
+        <v>312.7740143501274</v>
       </c>
       <c r="G29" t="n">
-        <v>184.9352392365969</v>
+        <v>184.935239236599</v>
       </c>
       <c r="H29" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="I29" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="J29" t="n">
-        <v>54.64</v>
+        <v>462.5007737914266</v>
       </c>
       <c r="K29" t="n">
-        <v>730.8099999999999</v>
+        <v>487.307422685899</v>
       </c>
       <c r="L29" t="n">
-        <v>1406.98</v>
+        <v>1163.477422685925</v>
       </c>
       <c r="M29" t="n">
-        <v>1952.071769583206</v>
+        <v>1708.569192269131</v>
       </c>
       <c r="N29" t="n">
-        <v>1952.071769583206</v>
+        <v>2028.070777832272</v>
       </c>
       <c r="O29" t="n">
-        <v>2244.582248558462</v>
+        <v>2704.240777832281</v>
       </c>
       <c r="P29" t="n">
-        <v>2272.341470726227</v>
+        <v>2732.000000000047</v>
       </c>
       <c r="Q29" t="n">
-        <v>2732</v>
+        <v>2732.000000000047</v>
       </c>
       <c r="R29" t="n">
-        <v>2732</v>
+        <v>2732.000000000047</v>
       </c>
       <c r="S29" t="n">
-        <v>2516.485480977299</v>
+        <v>2516.485480977346</v>
       </c>
       <c r="T29" t="n">
-        <v>2204.552874693434</v>
+        <v>2204.552874693481</v>
       </c>
       <c r="U29" t="n">
-        <v>1828.587685042282</v>
+        <v>1828.587685042329</v>
       </c>
       <c r="V29" t="n">
-        <v>1472.172509116197</v>
+        <v>1472.172509116244</v>
       </c>
       <c r="W29" t="n">
-        <v>1107.148796004129</v>
+        <v>1434.658780452348</v>
       </c>
       <c r="X29" t="n">
-        <v>1107.148796004129</v>
+        <v>1116.192282007229</v>
       </c>
       <c r="Y29" t="n">
-        <v>870.4645205669507</v>
+        <v>879.5080065700508</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>444.6705657350176</v>
+        <v>444.6705657350196</v>
       </c>
       <c r="C30" t="n">
-        <v>359.7211592243921</v>
+        <v>359.7211592243941</v>
       </c>
       <c r="D30" t="n">
-        <v>288.0669300347935</v>
+        <v>288.0669300347955</v>
       </c>
       <c r="E30" t="n">
-        <v>221.7314782954878</v>
+        <v>221.7314782954899</v>
       </c>
       <c r="F30" t="n">
-        <v>158.4625466410667</v>
+        <v>158.4625466410688</v>
       </c>
       <c r="G30" t="n">
-        <v>109.3371530566099</v>
+        <v>109.337153056612</v>
       </c>
       <c r="H30" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="I30" t="n">
-        <v>117.5073638166216</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="J30" t="n">
-        <v>251.3219397466375</v>
+        <v>383.121063141861</v>
       </c>
       <c r="K30" t="n">
-        <v>589.1628666890723</v>
+        <v>589.1628666890746</v>
       </c>
       <c r="L30" t="n">
-        <v>883.1688712088007</v>
+        <v>1157.398871208803</v>
       </c>
       <c r="M30" t="n">
-        <v>1269.91736295166</v>
+        <v>1269.917362951662</v>
       </c>
       <c r="N30" t="n">
-        <v>1430.335331427153</v>
+        <v>1430.335331427155</v>
       </c>
       <c r="O30" t="n">
-        <v>1694.203462073136</v>
+        <v>1694.203462073138</v>
       </c>
       <c r="P30" t="n">
-        <v>1826.657602580378</v>
+        <v>1826.657602580381</v>
       </c>
       <c r="Q30" t="n">
-        <v>1826.657602580378</v>
+        <v>1826.657602580381</v>
       </c>
       <c r="R30" t="n">
-        <v>1560.263677356515</v>
+        <v>1560.263677356517</v>
       </c>
       <c r="S30" t="n">
-        <v>1370.762352825843</v>
+        <v>1370.762352825845</v>
       </c>
       <c r="T30" t="n">
-        <v>1241.537156398775</v>
+        <v>1241.537156398777</v>
       </c>
       <c r="U30" t="n">
-        <v>1117.089251552389</v>
+        <v>1117.089251552391</v>
       </c>
       <c r="V30" t="n">
-        <v>978.1895877225702</v>
+        <v>978.1895877225722</v>
       </c>
       <c r="W30" t="n">
-        <v>821.2470191267838</v>
+        <v>821.2470191267859</v>
       </c>
       <c r="X30" t="n">
-        <v>676.9412217072004</v>
+        <v>676.9412217072024</v>
       </c>
       <c r="Y30" t="n">
-        <v>553.3135522464586</v>
+        <v>553.3135522464606</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>392.3225510796456</v>
+        <v>402.5385110160908</v>
       </c>
       <c r="C31" t="n">
-        <v>396.5545568980814</v>
+        <v>406.7705168345266</v>
       </c>
       <c r="D31" t="n">
-        <v>396.5545568980814</v>
+        <v>398.1480743541675</v>
       </c>
       <c r="E31" t="n">
-        <v>396.5545568980814</v>
+        <v>394.1269583572417</v>
       </c>
       <c r="F31" t="n">
-        <v>399.1455294900169</v>
+        <v>396.7179309491772</v>
       </c>
       <c r="G31" t="n">
-        <v>430.8695724260825</v>
+        <v>428.4419738852428</v>
       </c>
       <c r="H31" t="n">
-        <v>479.3939080772833</v>
+        <v>476.9663095364436</v>
       </c>
       <c r="I31" t="n">
-        <v>581.3874604559892</v>
+        <v>578.9598619151494</v>
       </c>
       <c r="J31" t="n">
-        <v>826.8858284854897</v>
+        <v>824.4582299446499</v>
       </c>
       <c r="K31" t="n">
-        <v>826.8858284854897</v>
+        <v>824.4582299446499</v>
       </c>
       <c r="L31" t="n">
-        <v>826.8858284854897</v>
+        <v>824.4582299446499</v>
       </c>
       <c r="M31" t="n">
-        <v>826.8858284854897</v>
+        <v>592.3565360291748</v>
       </c>
       <c r="N31" t="n">
-        <v>826.8858284854897</v>
+        <v>504.7704157451622</v>
       </c>
       <c r="O31" t="n">
-        <v>826.8858284854897</v>
+        <v>504.7704157451622</v>
       </c>
       <c r="P31" t="n">
-        <v>589.4508141865275</v>
+        <v>504.7704157451622</v>
       </c>
       <c r="Q31" t="n">
-        <v>589.4508141865275</v>
+        <v>504.7704157451622</v>
       </c>
       <c r="R31" t="n">
-        <v>139.3203984413675</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="S31" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="T31" t="n">
-        <v>121.3194447325753</v>
+        <v>121.3194447325775</v>
       </c>
       <c r="U31" t="n">
-        <v>246.1054088462718</v>
+        <v>246.1054088462739</v>
       </c>
       <c r="V31" t="n">
-        <v>323.1568017322178</v>
+        <v>323.1568017322199</v>
       </c>
       <c r="W31" t="n">
-        <v>373.2777199918952</v>
+        <v>373.2777199918973</v>
       </c>
       <c r="X31" t="n">
-        <v>402.5385110160887</v>
+        <v>402.5385110160908</v>
       </c>
       <c r="Y31" t="n">
-        <v>402.5385110160887</v>
+        <v>402.5385110160908</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>744.8219906712106</v>
+        <v>492.7242047382401</v>
       </c>
       <c r="C32" t="n">
-        <v>570.6052449712167</v>
+        <v>318.5074590382462</v>
       </c>
       <c r="D32" t="n">
-        <v>570.6052449712167</v>
+        <v>183.821443139408</v>
       </c>
       <c r="E32" t="n">
-        <v>441.9554574895312</v>
+        <v>183.821443139408</v>
       </c>
       <c r="F32" t="n">
-        <v>312.7740143501253</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="G32" t="n">
-        <v>184.9352392365969</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="H32" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="I32" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="J32" t="n">
-        <v>350.4964828688339</v>
+        <v>462.5007737914266</v>
       </c>
       <c r="K32" t="n">
-        <v>375.3031317633063</v>
+        <v>487.307422685899</v>
       </c>
       <c r="L32" t="n">
-        <v>1051.473131763306</v>
+        <v>920.3949013465721</v>
       </c>
       <c r="M32" t="n">
-        <v>1596.564901346513</v>
+        <v>920.3949013465721</v>
       </c>
       <c r="N32" t="n">
-        <v>2244.582248558462</v>
+        <v>1568.412248558521</v>
       </c>
       <c r="O32" t="n">
-        <v>2244.582248558462</v>
+        <v>2244.582248558538</v>
       </c>
       <c r="P32" t="n">
-        <v>2272.341470726227</v>
+        <v>2272.341470726303</v>
       </c>
       <c r="Q32" t="n">
-        <v>2732</v>
+        <v>2732.000000000076</v>
       </c>
       <c r="R32" t="n">
-        <v>2732</v>
+        <v>2732.000000000076</v>
       </c>
       <c r="S32" t="n">
-        <v>2516.485480977299</v>
+        <v>2516.485480977375</v>
       </c>
       <c r="T32" t="n">
-        <v>2204.552874693434</v>
+        <v>2204.55287469351</v>
       </c>
       <c r="U32" t="n">
-        <v>1828.587685042282</v>
+        <v>1828.587685042358</v>
       </c>
       <c r="V32" t="n">
-        <v>1828.587685042282</v>
+        <v>1472.172509116273</v>
       </c>
       <c r="W32" t="n">
-        <v>1507.042777639947</v>
+        <v>1107.148796004205</v>
       </c>
       <c r="X32" t="n">
-        <v>1188.576279194828</v>
+        <v>936.4784932618571</v>
       </c>
       <c r="Y32" t="n">
-        <v>951.8920037576495</v>
+        <v>699.794217824679</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>444.6705657350176</v>
+        <v>444.6705657350196</v>
       </c>
       <c r="C33" t="n">
-        <v>359.7211592243921</v>
+        <v>359.7211592243941</v>
       </c>
       <c r="D33" t="n">
-        <v>288.0669300347935</v>
+        <v>288.0669300347955</v>
       </c>
       <c r="E33" t="n">
-        <v>221.7314782954878</v>
+        <v>221.7314782954899</v>
       </c>
       <c r="F33" t="n">
-        <v>158.4625466410667</v>
+        <v>158.4625466410688</v>
       </c>
       <c r="G33" t="n">
-        <v>109.3371530566099</v>
+        <v>109.337153056612</v>
       </c>
       <c r="H33" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="I33" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="J33" t="n">
-        <v>188.4545759300159</v>
+        <v>188.4545759300181</v>
       </c>
       <c r="K33" t="n">
-        <v>668.7263794772296</v>
+        <v>394.4963794772316</v>
       </c>
       <c r="L33" t="n">
-        <v>1157.398871208801</v>
+        <v>688.5023839969601</v>
       </c>
       <c r="M33" t="n">
-        <v>1269.91736295166</v>
+        <v>801.0208757398193</v>
       </c>
       <c r="N33" t="n">
-        <v>1430.335331427153</v>
+        <v>1156.105331427155</v>
       </c>
       <c r="O33" t="n">
-        <v>1694.203462073136</v>
+        <v>1694.203462073138</v>
       </c>
       <c r="P33" t="n">
-        <v>1826.657602580378</v>
+        <v>1826.657602580381</v>
       </c>
       <c r="Q33" t="n">
-        <v>1826.657602580378</v>
+        <v>1826.657602580381</v>
       </c>
       <c r="R33" t="n">
-        <v>1560.263677356515</v>
+        <v>1560.263677356517</v>
       </c>
       <c r="S33" t="n">
-        <v>1370.762352825843</v>
+        <v>1370.762352825845</v>
       </c>
       <c r="T33" t="n">
-        <v>1241.537156398775</v>
+        <v>1241.537156398777</v>
       </c>
       <c r="U33" t="n">
-        <v>1117.089251552389</v>
+        <v>1117.089251552391</v>
       </c>
       <c r="V33" t="n">
-        <v>978.1895877225702</v>
+        <v>978.1895877225722</v>
       </c>
       <c r="W33" t="n">
-        <v>821.2470191267838</v>
+        <v>821.2470191267859</v>
       </c>
       <c r="X33" t="n">
-        <v>676.9412217072004</v>
+        <v>676.9412217072024</v>
       </c>
       <c r="Y33" t="n">
-        <v>553.3135522464586</v>
+        <v>553.3135522464606</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>392.3225510796456</v>
+        <v>392.3225510796477</v>
       </c>
       <c r="C34" t="n">
-        <v>396.5545568980814</v>
+        <v>396.5545568980835</v>
       </c>
       <c r="D34" t="n">
-        <v>387.9321144177223</v>
+        <v>396.5545568980835</v>
       </c>
       <c r="E34" t="n">
-        <v>387.9321144177223</v>
+        <v>396.5545568980835</v>
       </c>
       <c r="F34" t="n">
-        <v>390.5230870096578</v>
+        <v>399.145529490019</v>
       </c>
       <c r="G34" t="n">
-        <v>422.2471299457234</v>
+        <v>430.8695724260846</v>
       </c>
       <c r="H34" t="n">
-        <v>470.7714655969242</v>
+        <v>479.3939080772854</v>
       </c>
       <c r="I34" t="n">
-        <v>572.76501797563</v>
+        <v>581.3874604559912</v>
       </c>
       <c r="J34" t="n">
-        <v>818.2633860051305</v>
+        <v>826.8858284854917</v>
       </c>
       <c r="K34" t="n">
-        <v>818.2633860051305</v>
+        <v>826.8858284854917</v>
       </c>
       <c r="L34" t="n">
-        <v>818.2633860051305</v>
+        <v>826.8858284854917</v>
       </c>
       <c r="M34" t="n">
-        <v>818.2633860051305</v>
+        <v>594.7841345700166</v>
       </c>
       <c r="N34" t="n">
-        <v>534.764916199322</v>
+        <v>311.285664764208</v>
       </c>
       <c r="O34" t="n">
-        <v>534.764916199322</v>
+        <v>311.285664764208</v>
       </c>
       <c r="P34" t="n">
-        <v>534.764916199322</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="Q34" t="n">
-        <v>139.3203984413675</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="R34" t="n">
-        <v>139.3203984413675</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="S34" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="T34" t="n">
-        <v>121.3194447325753</v>
+        <v>121.3194447325775</v>
       </c>
       <c r="U34" t="n">
-        <v>246.1054088462718</v>
+        <v>246.1054088462739</v>
       </c>
       <c r="V34" t="n">
-        <v>323.1568017322178</v>
+        <v>323.1568017322199</v>
       </c>
       <c r="W34" t="n">
-        <v>373.2777199918952</v>
+        <v>373.2777199918973</v>
       </c>
       <c r="X34" t="n">
-        <v>402.5385110160887</v>
+        <v>402.5385110160908</v>
       </c>
       <c r="Y34" t="n">
-        <v>402.5385110160887</v>
+        <v>402.5385110160908</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>870.4645205669507</v>
+        <v>705.2912608700569</v>
       </c>
       <c r="C35" t="n">
-        <v>696.2477748669569</v>
+        <v>705.2912608700569</v>
       </c>
       <c r="D35" t="n">
-        <v>561.5617589681187</v>
+        <v>570.6052449712188</v>
       </c>
       <c r="E35" t="n">
-        <v>432.9119714864332</v>
+        <v>441.9554574895333</v>
       </c>
       <c r="F35" t="n">
-        <v>303.7305283470273</v>
+        <v>312.7740143501274</v>
       </c>
       <c r="G35" t="n">
-        <v>184.9352392365969</v>
+        <v>184.935239236599</v>
       </c>
       <c r="H35" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="I35" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="J35" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="K35" t="n">
-        <v>730.8099999999999</v>
+        <v>79.44664889447446</v>
       </c>
       <c r="L35" t="n">
-        <v>761.5848415075377</v>
+        <v>755.6166488945005</v>
       </c>
       <c r="M35" t="n">
-        <v>761.5848415075377</v>
+        <v>920.0014707262849</v>
       </c>
       <c r="N35" t="n">
-        <v>1379.659999999992</v>
+        <v>920.0014707262849</v>
       </c>
       <c r="O35" t="n">
-        <v>2055.829999999996</v>
+        <v>1596.171470726309</v>
       </c>
       <c r="P35" t="n">
-        <v>2732</v>
+        <v>2272.341470726332</v>
       </c>
       <c r="Q35" t="n">
-        <v>2732</v>
+        <v>2732.000000000105</v>
       </c>
       <c r="R35" t="n">
-        <v>2732</v>
+        <v>2732.000000000105</v>
       </c>
       <c r="S35" t="n">
-        <v>2516.485480977299</v>
+        <v>2732.000000000105</v>
       </c>
       <c r="T35" t="n">
-        <v>2204.552874693434</v>
+        <v>2420.06739371624</v>
       </c>
       <c r="U35" t="n">
-        <v>1828.587685042282</v>
+        <v>2188.950936876946</v>
       </c>
       <c r="V35" t="n">
-        <v>1472.172509116197</v>
+        <v>1832.535760950861</v>
       </c>
       <c r="W35" t="n">
-        <v>1107.148796004129</v>
+        <v>1467.512047838793</v>
       </c>
       <c r="X35" t="n">
-        <v>1107.148796004129</v>
+        <v>1149.045549393674</v>
       </c>
       <c r="Y35" t="n">
-        <v>870.4645205669507</v>
+        <v>912.3612739564958</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>444.6705657350175</v>
+        <v>444.6705657350196</v>
       </c>
       <c r="C36" t="n">
-        <v>359.721159224392</v>
+        <v>359.7211592243941</v>
       </c>
       <c r="D36" t="n">
-        <v>288.0669300347934</v>
+        <v>288.0669300347955</v>
       </c>
       <c r="E36" t="n">
-        <v>221.7314782954877</v>
+        <v>221.7314782954898</v>
       </c>
       <c r="F36" t="n">
-        <v>158.4625466410666</v>
+        <v>158.4625466410687</v>
       </c>
       <c r="G36" t="n">
-        <v>109.3371530566098</v>
+        <v>109.337153056612</v>
       </c>
       <c r="H36" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="I36" t="n">
-        <v>54.64</v>
+        <v>117.5073638166237</v>
       </c>
       <c r="J36" t="n">
-        <v>188.4545759300159</v>
+        <v>525.5519397466396</v>
       </c>
       <c r="K36" t="n">
-        <v>394.4963794772295</v>
+        <v>863.3928666890746</v>
       </c>
       <c r="L36" t="n">
-        <v>962.732383996958</v>
+        <v>1157.398871208803</v>
       </c>
       <c r="M36" t="n">
-        <v>1075.250875739817</v>
+        <v>1269.917362951662</v>
       </c>
       <c r="N36" t="n">
-        <v>1430.335331427153</v>
+        <v>1430.335331427155</v>
       </c>
       <c r="O36" t="n">
-        <v>1694.203462073136</v>
+        <v>1694.203462073138</v>
       </c>
       <c r="P36" t="n">
-        <v>1826.657602580378</v>
+        <v>1826.657602580381</v>
       </c>
       <c r="Q36" t="n">
-        <v>1826.657602580378</v>
+        <v>1826.657602580381</v>
       </c>
       <c r="R36" t="n">
-        <v>1560.263677356515</v>
+        <v>1560.263677356517</v>
       </c>
       <c r="S36" t="n">
-        <v>1370.762352825842</v>
+        <v>1370.762352825845</v>
       </c>
       <c r="T36" t="n">
-        <v>1241.537156398775</v>
+        <v>1241.537156398777</v>
       </c>
       <c r="U36" t="n">
-        <v>1117.089251552388</v>
+        <v>1117.089251552391</v>
       </c>
       <c r="V36" t="n">
-        <v>978.1895877225701</v>
+        <v>978.1895877225722</v>
       </c>
       <c r="W36" t="n">
-        <v>821.2470191267837</v>
+        <v>821.2470191267859</v>
       </c>
       <c r="X36" t="n">
-        <v>676.9412217072003</v>
+        <v>676.9412217072024</v>
       </c>
       <c r="Y36" t="n">
-        <v>553.3135522464585</v>
+        <v>553.3135522464606</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>391.9674475317833</v>
+        <v>392.3225510796477</v>
       </c>
       <c r="C37" t="n">
-        <v>396.1994533502191</v>
+        <v>396.5545568980835</v>
       </c>
       <c r="D37" t="n">
-        <v>396.1994533502191</v>
+        <v>387.9321144177244</v>
       </c>
       <c r="E37" t="n">
-        <v>392.1783373532933</v>
+        <v>387.9321144177244</v>
       </c>
       <c r="F37" t="n">
-        <v>394.7693099452288</v>
+        <v>390.5230870096599</v>
       </c>
       <c r="G37" t="n">
-        <v>426.4933528812944</v>
+        <v>422.2471299457255</v>
       </c>
       <c r="H37" t="n">
-        <v>475.0176885324952</v>
+        <v>470.7714655969263</v>
       </c>
       <c r="I37" t="n">
-        <v>577.0112409112011</v>
+        <v>572.7650179756322</v>
       </c>
       <c r="J37" t="n">
-        <v>822.5096089407016</v>
+        <v>818.2633860051327</v>
       </c>
       <c r="K37" t="n">
-        <v>822.5096089407016</v>
+        <v>818.2633860051327</v>
       </c>
       <c r="L37" t="n">
-        <v>822.5096089407016</v>
+        <v>818.2633860051327</v>
       </c>
       <c r="M37" t="n">
-        <v>822.5096089407016</v>
+        <v>818.2633860051327</v>
       </c>
       <c r="N37" t="n">
-        <v>812.9402673595766</v>
+        <v>818.2633860051327</v>
       </c>
       <c r="O37" t="n">
-        <v>458.4390683395417</v>
+        <v>463.7621869850977</v>
       </c>
       <c r="P37" t="n">
-        <v>54.64</v>
+        <v>463.7621869850977</v>
       </c>
       <c r="Q37" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="R37" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="S37" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="T37" t="n">
-        <v>121.3194447325754</v>
+        <v>121.3194447325775</v>
       </c>
       <c r="U37" t="n">
-        <v>246.1054088462718</v>
+        <v>246.1054088462739</v>
       </c>
       <c r="V37" t="n">
-        <v>323.1568017322178</v>
+        <v>323.1568017322199</v>
       </c>
       <c r="W37" t="n">
-        <v>373.2777199918952</v>
+        <v>373.2777199918973</v>
       </c>
       <c r="X37" t="n">
-        <v>402.5385110160887</v>
+        <v>402.5385110160908</v>
       </c>
       <c r="Y37" t="n">
-        <v>391.9674475317833</v>
+        <v>402.5385110160908</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>749.2127673334519</v>
+        <v>749.2127673334539</v>
       </c>
       <c r="C38" t="n">
-        <v>574.996021633458</v>
+        <v>574.9960216334601</v>
       </c>
       <c r="D38" t="n">
-        <v>440.3100057346198</v>
+        <v>440.3100057346219</v>
       </c>
       <c r="E38" t="n">
-        <v>311.6602182529343</v>
+        <v>311.6602182529364</v>
       </c>
       <c r="F38" t="n">
-        <v>182.4787751135284</v>
+        <v>182.4787751135305</v>
       </c>
       <c r="G38" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="H38" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="I38" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="J38" t="n">
-        <v>54.64</v>
+        <v>462.5007737914266</v>
       </c>
       <c r="K38" t="n">
-        <v>730.8099999999999</v>
+        <v>487.307422685899</v>
       </c>
       <c r="L38" t="n">
-        <v>1406.98</v>
+        <v>518.0822641934366</v>
       </c>
       <c r="M38" t="n">
-        <v>1406.98</v>
+        <v>920.0014707262703</v>
       </c>
       <c r="N38" t="n">
-        <v>1568.412248558458</v>
+        <v>920.0014707262703</v>
       </c>
       <c r="O38" t="n">
-        <v>2244.582248558462</v>
+        <v>1596.171470726301</v>
       </c>
       <c r="P38" t="n">
-        <v>2272.341470726227</v>
+        <v>2272.341470726332</v>
       </c>
       <c r="Q38" t="n">
-        <v>2732</v>
+        <v>2732.000000000105</v>
       </c>
       <c r="R38" t="n">
-        <v>2732</v>
+        <v>2732.000000000105</v>
       </c>
       <c r="S38" t="n">
-        <v>2516.485480977299</v>
+        <v>2516.485480977404</v>
       </c>
       <c r="T38" t="n">
-        <v>2204.552874693434</v>
+        <v>2204.552874693539</v>
       </c>
       <c r="U38" t="n">
-        <v>1914.405944895222</v>
+        <v>1828.587685042387</v>
       </c>
       <c r="V38" t="n">
-        <v>1557.990768969137</v>
+        <v>1472.172509116302</v>
       </c>
       <c r="W38" t="n">
-        <v>1192.967055857069</v>
+        <v>1107.148796004234</v>
       </c>
       <c r="X38" t="n">
-        <v>1192.967055857069</v>
+        <v>1107.148796004234</v>
       </c>
       <c r="Y38" t="n">
-        <v>956.2827804198907</v>
+        <v>870.4645205670557</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>444.6705657350176</v>
+        <v>444.6705657350196</v>
       </c>
       <c r="C39" t="n">
-        <v>359.7211592243921</v>
+        <v>359.7211592243941</v>
       </c>
       <c r="D39" t="n">
-        <v>288.0669300347935</v>
+        <v>288.0669300347955</v>
       </c>
       <c r="E39" t="n">
-        <v>221.7314782954878</v>
+        <v>221.7314782954898</v>
       </c>
       <c r="F39" t="n">
-        <v>158.4625466410667</v>
+        <v>158.4625466410687</v>
       </c>
       <c r="G39" t="n">
-        <v>109.3371530566099</v>
+        <v>109.337153056612</v>
       </c>
       <c r="H39" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="I39" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="J39" t="n">
-        <v>188.4545759300159</v>
+        <v>188.4545759300181</v>
       </c>
       <c r="K39" t="n">
-        <v>668.7263794772296</v>
+        <v>589.1628666890743</v>
       </c>
       <c r="L39" t="n">
-        <v>1157.398871208801</v>
+        <v>883.1688712088028</v>
       </c>
       <c r="M39" t="n">
-        <v>1269.91736295166</v>
+        <v>995.6873629516621</v>
       </c>
       <c r="N39" t="n">
-        <v>1430.335331427153</v>
+        <v>1430.335331427155</v>
       </c>
       <c r="O39" t="n">
-        <v>1694.203462073136</v>
+        <v>1694.203462073138</v>
       </c>
       <c r="P39" t="n">
-        <v>1826.657602580378</v>
+        <v>1826.657602580381</v>
       </c>
       <c r="Q39" t="n">
-        <v>1826.657602580378</v>
+        <v>1826.657602580381</v>
       </c>
       <c r="R39" t="n">
-        <v>1560.263677356515</v>
+        <v>1560.263677356517</v>
       </c>
       <c r="S39" t="n">
-        <v>1370.762352825843</v>
+        <v>1370.762352825845</v>
       </c>
       <c r="T39" t="n">
-        <v>1241.537156398775</v>
+        <v>1241.537156398777</v>
       </c>
       <c r="U39" t="n">
-        <v>1117.089251552389</v>
+        <v>1117.089251552391</v>
       </c>
       <c r="V39" t="n">
-        <v>978.1895877225702</v>
+        <v>978.1895877225722</v>
       </c>
       <c r="W39" t="n">
-        <v>821.2470191267838</v>
+        <v>821.2470191267859</v>
       </c>
       <c r="X39" t="n">
-        <v>676.9412217072004</v>
+        <v>676.9412217072024</v>
       </c>
       <c r="Y39" t="n">
-        <v>553.3135522464586</v>
+        <v>553.3135522464606</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>391.9674475317833</v>
+        <v>391.9674475317854</v>
       </c>
       <c r="C40" t="n">
-        <v>396.1994533502191</v>
+        <v>396.1994533502212</v>
       </c>
       <c r="D40" t="n">
-        <v>387.57701086986</v>
+        <v>396.1994533502212</v>
       </c>
       <c r="E40" t="n">
-        <v>387.57701086986</v>
+        <v>396.1994533502212</v>
       </c>
       <c r="F40" t="n">
-        <v>390.1679834617955</v>
+        <v>398.7904259421567</v>
       </c>
       <c r="G40" t="n">
-        <v>421.8920263978611</v>
+        <v>430.5144688782223</v>
       </c>
       <c r="H40" t="n">
-        <v>470.4163620490619</v>
+        <v>479.0388045294231</v>
       </c>
       <c r="I40" t="n">
-        <v>572.4099144277677</v>
+        <v>581.0323569081289</v>
       </c>
       <c r="J40" t="n">
-        <v>817.9082824572682</v>
+        <v>826.5307249376294</v>
       </c>
       <c r="K40" t="n">
-        <v>817.9082824572682</v>
+        <v>825.2631772994488</v>
       </c>
       <c r="L40" t="n">
-        <v>817.9082824572682</v>
+        <v>825.2631772994488</v>
       </c>
       <c r="M40" t="n">
-        <v>817.9082824572682</v>
+        <v>593.1614833839736</v>
       </c>
       <c r="N40" t="n">
-        <v>585.219657457123</v>
+        <v>309.663013578165</v>
       </c>
       <c r="O40" t="n">
-        <v>585.219657457123</v>
+        <v>139.3203984413696</v>
       </c>
       <c r="P40" t="n">
-        <v>585.219657457123</v>
+        <v>139.3203984413696</v>
       </c>
       <c r="Q40" t="n">
-        <v>139.3203984413675</v>
+        <v>139.3203984413696</v>
       </c>
       <c r="R40" t="n">
-        <v>139.3203984413675</v>
+        <v>139.3203984413696</v>
       </c>
       <c r="S40" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="T40" t="n">
-        <v>121.3194447325753</v>
+        <v>121.3194447325775</v>
       </c>
       <c r="U40" t="n">
-        <v>246.1054088462718</v>
+        <v>246.1054088462739</v>
       </c>
       <c r="V40" t="n">
-        <v>323.1568017322178</v>
+        <v>323.1568017322199</v>
       </c>
       <c r="W40" t="n">
-        <v>373.2777199918952</v>
+        <v>373.2777199918973</v>
       </c>
       <c r="X40" t="n">
-        <v>402.5385110160887</v>
+        <v>402.5385110160908</v>
       </c>
       <c r="Y40" t="n">
-        <v>391.9674475317833</v>
+        <v>391.9674475317854</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1227.243475184483</v>
+        <v>332.7847369766371</v>
       </c>
       <c r="C41" t="n">
-        <v>903.5317799895399</v>
+        <v>332.7847369766371</v>
       </c>
       <c r="D41" t="n">
-        <v>903.5317799895399</v>
+        <v>332.7847369766371</v>
       </c>
       <c r="E41" t="n">
-        <v>625.387043012905</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="F41" t="n">
-        <v>625.387043012905</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="G41" t="n">
-        <v>348.0533184044272</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="H41" t="n">
-        <v>68.26312967288075</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="I41" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="J41" t="n">
-        <v>54.64</v>
+        <v>462.5007737914266</v>
       </c>
       <c r="K41" t="n">
-        <v>703.8834306202814</v>
+        <v>1020.30485963555</v>
       </c>
       <c r="L41" t="n">
-        <v>1380.053430620281</v>
+        <v>1051.079701143088</v>
       </c>
       <c r="M41" t="n">
-        <v>1380.053430620281</v>
+        <v>1596.171470726294</v>
       </c>
       <c r="N41" t="n">
-        <v>2028.07077783223</v>
+        <v>1596.171470726294</v>
       </c>
       <c r="O41" t="n">
-        <v>2704.240777832234</v>
+        <v>1596.171470726294</v>
       </c>
       <c r="P41" t="n">
-        <v>2732</v>
+        <v>2272.341470726332</v>
       </c>
       <c r="Q41" t="n">
-        <v>2732</v>
+        <v>2732.000000000105</v>
       </c>
       <c r="R41" t="n">
-        <v>2732</v>
+        <v>2621.389146912289</v>
       </c>
       <c r="S41" t="n">
-        <v>2732</v>
+        <v>2256.379678394639</v>
       </c>
       <c r="T41" t="n">
-        <v>2726.575187691688</v>
+        <v>1794.952122615825</v>
       </c>
       <c r="U41" t="n">
-        <v>2201.115048545586</v>
+        <v>1794.952122615825</v>
       </c>
       <c r="V41" t="n">
-        <v>1695.204923124552</v>
+        <v>1794.952122615825</v>
       </c>
       <c r="W41" t="n">
-        <v>1695.204923124552</v>
+        <v>1280.433460008807</v>
       </c>
       <c r="X41" t="n">
-        <v>1227.243475184483</v>
+        <v>812.4720120687384</v>
       </c>
       <c r="Y41" t="n">
-        <v>1227.243475184483</v>
+        <v>426.2927871366107</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>617.807460136774</v>
+        <v>1010.035402545648</v>
       </c>
       <c r="C42" t="n">
-        <v>479.9812812361075</v>
+        <v>775.5910465400732</v>
       </c>
       <c r="D42" t="n">
-        <v>258.8321025515594</v>
+        <v>554.4418678555251</v>
       </c>
       <c r="E42" t="n">
-        <v>258.8321025515594</v>
+        <v>338.6114666212699</v>
       </c>
       <c r="F42" t="n">
-        <v>258.8321025515594</v>
+        <v>338.6114666212699</v>
       </c>
       <c r="G42" t="n">
-        <v>258.8321025515594</v>
+        <v>139.9911235418636</v>
       </c>
       <c r="H42" t="n">
-        <v>54.64</v>
+        <v>139.9911235418636</v>
       </c>
       <c r="I42" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="J42" t="n">
-        <v>316.1645759300159</v>
+        <v>316.164575930018</v>
       </c>
       <c r="K42" t="n">
-        <v>584.8565681564749</v>
+        <v>649.9163794772317</v>
       </c>
       <c r="L42" t="n">
-        <v>1006.572572676203</v>
+        <v>1071.63238399696</v>
       </c>
       <c r="M42" t="n">
-        <v>1246.801064419063</v>
+        <v>1184.150875739819</v>
       </c>
       <c r="N42" t="n">
-        <v>1534.929032894556</v>
+        <v>1472.278844215312</v>
       </c>
       <c r="O42" t="n">
-        <v>1798.797163540539</v>
+        <v>1863.856974861295</v>
       </c>
       <c r="P42" t="n">
-        <v>2058.961304047781</v>
+        <v>2058.961304047783</v>
       </c>
       <c r="Q42" t="n">
-        <v>2028.026426026142</v>
+        <v>2058.961304047783</v>
       </c>
       <c r="R42" t="n">
-        <v>2028.026426026142</v>
+        <v>1835.288097798824</v>
       </c>
       <c r="S42" t="n">
-        <v>2028.026426026142</v>
+        <v>1835.288097798824</v>
       </c>
       <c r="T42" t="n">
-        <v>1749.306280104125</v>
+        <v>1556.567951876807</v>
       </c>
       <c r="U42" t="n">
-        <v>1749.306280104125</v>
+        <v>1556.567951876807</v>
       </c>
       <c r="V42" t="n">
-        <v>1749.306280104125</v>
+        <v>1268.173338552039</v>
       </c>
       <c r="W42" t="n">
-        <v>1442.868762013389</v>
+        <v>1268.173338552039</v>
       </c>
       <c r="X42" t="n">
-        <v>1149.068015098856</v>
+        <v>1268.173338552039</v>
       </c>
       <c r="Y42" t="n">
-        <v>875.9453961431645</v>
+        <v>1268.173338552039</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="C43" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="D43" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="E43" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="F43" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="G43" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="H43" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="I43" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="J43" t="n">
-        <v>153.6183680295005</v>
+        <v>153.6183680295026</v>
       </c>
       <c r="K43" t="n">
-        <v>153.6183680295005</v>
+        <v>153.6183680295026</v>
       </c>
       <c r="L43" t="n">
-        <v>153.6183680295005</v>
+        <v>153.6183680295026</v>
       </c>
       <c r="M43" t="n">
-        <v>153.6183680295005</v>
+        <v>153.6183680295026</v>
       </c>
       <c r="N43" t="n">
-        <v>153.6183680295005</v>
+        <v>153.6183680295026</v>
       </c>
       <c r="O43" t="n">
-        <v>153.6183680295005</v>
+        <v>153.6183680295026</v>
       </c>
       <c r="P43" t="n">
-        <v>153.6183680295005</v>
+        <v>153.6183680295026</v>
       </c>
       <c r="Q43" t="n">
-        <v>153.6183680295005</v>
+        <v>153.6183680295026</v>
       </c>
       <c r="R43" t="n">
-        <v>153.6183680295005</v>
+        <v>153.6183680295026</v>
       </c>
       <c r="S43" t="n">
-        <v>153.6183680295005</v>
+        <v>153.6183680295026</v>
       </c>
       <c r="T43" t="n">
-        <v>72.15672608742862</v>
+        <v>153.6183680295026</v>
       </c>
       <c r="U43" t="n">
-        <v>72.15672608742862</v>
+        <v>153.6183680295026</v>
       </c>
       <c r="V43" t="n">
-        <v>72.15672608742862</v>
+        <v>82.73926680100141</v>
       </c>
       <c r="W43" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="X43" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
       <c r="Y43" t="n">
-        <v>54.64</v>
+        <v>54.6400000000021</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>461.0999780232262</v>
+        <v>1124.114398941739</v>
       </c>
       <c r="C44" t="n">
-        <v>54.56</v>
+        <v>779.7110536386313</v>
       </c>
       <c r="D44" t="n">
-        <v>54.56</v>
+        <v>413.7119064266618</v>
       </c>
       <c r="E44" t="n">
-        <v>54.56</v>
+        <v>413.7119064266618</v>
       </c>
       <c r="F44" t="n">
-        <v>54.56</v>
+        <v>413.7119064266618</v>
       </c>
       <c r="G44" t="n">
-        <v>54.56</v>
+        <v>54.56000000000211</v>
       </c>
       <c r="H44" t="n">
-        <v>54.56</v>
+        <v>54.56000000000211</v>
       </c>
       <c r="I44" t="n">
-        <v>54.56</v>
+        <v>54.56000000000211</v>
       </c>
       <c r="J44" t="n">
-        <v>54.56</v>
+        <v>54.56000000000211</v>
       </c>
       <c r="K44" t="n">
-        <v>729.7399999999999</v>
+        <v>79.36664889447447</v>
       </c>
       <c r="L44" t="n">
-        <v>1404.802652788047</v>
+        <v>754.5466488945004</v>
       </c>
       <c r="M44" t="n">
-        <v>1404.802652788047</v>
+        <v>1299.638418477707</v>
       </c>
       <c r="N44" t="n">
-        <v>2052.819999999996</v>
+        <v>1565.402248558541</v>
       </c>
       <c r="O44" t="n">
-        <v>2052.819999999996</v>
+        <v>2240.582248558567</v>
       </c>
       <c r="P44" t="n">
-        <v>2728</v>
+        <v>2268.341470726332</v>
       </c>
       <c r="Q44" t="n">
-        <v>2728</v>
+        <v>2728.000000000105</v>
       </c>
       <c r="R44" t="n">
-        <v>2564.030590814188</v>
+        <v>2728.000000000105</v>
       </c>
       <c r="S44" t="n">
-        <v>2116.192839468255</v>
+        <v>2281.172349664273</v>
       </c>
       <c r="T44" t="n">
-        <v>2116.192839468255</v>
+        <v>2281.172349664273</v>
       </c>
       <c r="U44" t="n">
-        <v>2116.192839468255</v>
+        <v>1673.894028699989</v>
       </c>
       <c r="V44" t="n">
-        <v>1527.454431218937</v>
+        <v>1673.894028699989</v>
       </c>
       <c r="W44" t="n">
-        <v>930.1074857836368</v>
+        <v>1673.894028699989</v>
       </c>
       <c r="X44" t="n">
-        <v>930.1074857836368</v>
+        <v>1124.114398941739</v>
       </c>
       <c r="Y44" t="n">
-        <v>461.0999780232262</v>
+        <v>1124.114398941739</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1117.052835089345</v>
+        <v>824.0021275535435</v>
       </c>
       <c r="C45" t="n">
-        <v>799.7801962554869</v>
+        <v>507.7395897297866</v>
       </c>
       <c r="D45" t="n">
-        <v>799.7801962554869</v>
+        <v>507.7395897297866</v>
       </c>
       <c r="E45" t="n">
-        <v>799.7801962554869</v>
+        <v>507.7395897297866</v>
       </c>
       <c r="F45" t="n">
-        <v>504.1880322778335</v>
+        <v>507.7395897297866</v>
       </c>
       <c r="G45" t="n">
-        <v>222.7394063701443</v>
+        <v>507.7395897297866</v>
       </c>
       <c r="H45" t="n">
-        <v>222.7394063701443</v>
+        <v>221.7293053600454</v>
       </c>
       <c r="I45" t="n">
-        <v>54.56</v>
+        <v>54.56000000000211</v>
       </c>
       <c r="J45" t="n">
-        <v>234.9045759300159</v>
+        <v>235.894575930018</v>
       </c>
       <c r="K45" t="n">
-        <v>487.4763794772296</v>
+        <v>489.4563794772316</v>
       </c>
       <c r="L45" t="n">
-        <v>804.3084217328071</v>
+        <v>830.9823839969602</v>
       </c>
       <c r="M45" t="n">
-        <v>963.3569134756664</v>
+        <v>943.5008757398193</v>
       </c>
       <c r="N45" t="n">
-        <v>1170.304881951159</v>
+        <v>1127.23054232852</v>
       </c>
       <c r="O45" t="n">
-        <v>1480.703012597142</v>
+        <v>1438.618672974503</v>
       </c>
       <c r="P45" t="n">
-        <v>1613.157153104385</v>
+        <v>1618.592813481745</v>
       </c>
       <c r="Q45" t="n">
-        <v>1613.157153104385</v>
+        <v>1505.839753641924</v>
       </c>
       <c r="R45" t="n">
-        <v>1613.157153104385</v>
+        <v>1505.839753641924</v>
       </c>
       <c r="S45" t="n">
-        <v>1613.157153104385</v>
+        <v>1505.839753641924</v>
       </c>
       <c r="T45" t="n">
-        <v>1251.608724354085</v>
+        <v>1505.839753641924</v>
       </c>
       <c r="U45" t="n">
-        <v>1251.608724354085</v>
+        <v>1178.942928327417</v>
       </c>
       <c r="V45" t="n">
-        <v>1251.608724354085</v>
+        <v>1178.942928327417</v>
       </c>
       <c r="W45" t="n">
-        <v>1251.608724354085</v>
+        <v>1178.942928327417</v>
       </c>
       <c r="X45" t="n">
-        <v>1117.052835089345</v>
+        <v>1178.942928327417</v>
       </c>
       <c r="Y45" t="n">
-        <v>1117.052835089345</v>
+        <v>824.0021275535435</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>54.56</v>
+        <v>73.34836802950261</v>
       </c>
       <c r="C46" t="n">
-        <v>54.56</v>
+        <v>73.34836802950261</v>
       </c>
       <c r="D46" t="n">
-        <v>54.56</v>
+        <v>73.34836802950261</v>
       </c>
       <c r="E46" t="n">
-        <v>54.56</v>
+        <v>73.34836802950261</v>
       </c>
       <c r="F46" t="n">
-        <v>54.56</v>
+        <v>73.34836802950261</v>
       </c>
       <c r="G46" t="n">
-        <v>54.56</v>
+        <v>73.34836802950261</v>
       </c>
       <c r="H46" t="n">
-        <v>54.56</v>
+        <v>73.34836802950261</v>
       </c>
       <c r="I46" t="n">
-        <v>54.56</v>
+        <v>54.56000000000211</v>
       </c>
       <c r="J46" t="n">
-        <v>72.3583680295005</v>
+        <v>73.34836802950261</v>
       </c>
       <c r="K46" t="n">
-        <v>72.3583680295005</v>
+        <v>73.34836802950261</v>
       </c>
       <c r="L46" t="n">
-        <v>72.3583680295005</v>
+        <v>73.34836802950261</v>
       </c>
       <c r="M46" t="n">
-        <v>72.3583680295005</v>
+        <v>73.34836802950261</v>
       </c>
       <c r="N46" t="n">
-        <v>72.3583680295005</v>
+        <v>73.34836802950261</v>
       </c>
       <c r="O46" t="n">
-        <v>72.3583680295005</v>
+        <v>73.34836802950261</v>
       </c>
       <c r="P46" t="n">
-        <v>72.3583680295005</v>
+        <v>73.34836802950261</v>
       </c>
       <c r="Q46" t="n">
-        <v>72.3583680295005</v>
+        <v>73.34836802950261</v>
       </c>
       <c r="R46" t="n">
-        <v>72.3583680295005</v>
+        <v>73.34836802950261</v>
       </c>
       <c r="S46" t="n">
-        <v>72.3583680295005</v>
+        <v>73.34836802950261</v>
       </c>
       <c r="T46" t="n">
-        <v>54.56</v>
+        <v>73.34836802950261</v>
       </c>
       <c r="U46" t="n">
-        <v>54.56</v>
+        <v>73.34836802950261</v>
       </c>
       <c r="V46" t="n">
-        <v>54.56</v>
+        <v>73.34836802950261</v>
       </c>
       <c r="W46" t="n">
-        <v>54.56</v>
+        <v>73.34836802950261</v>
       </c>
       <c r="X46" t="n">
-        <v>54.56</v>
+        <v>73.34836802950261</v>
       </c>
       <c r="Y46" t="n">
-        <v>54.56</v>
+        <v>73.34836802950261</v>
       </c>
     </row>
   </sheetData>
@@ -7964,13 +7964,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>430.3047365861567</v>
+        <v>18.32415699885917</v>
       </c>
       <c r="K2" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L2" t="n">
-        <v>234.0366244460561</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>1060.271045550332</v>
@@ -7979,10 +7979,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O2" t="n">
-        <v>37.05812585549948</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>683.0753298888525</v>
       </c>
       <c r="Q2" t="n">
         <v>615.8520732695737</v>
@@ -8201,25 +8201,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>18.32415699885917</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K5" t="n">
-        <v>716.8751175230994</v>
+        <v>525.8158820231831</v>
       </c>
       <c r="L5" t="n">
-        <v>587.4623945474083</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>509.6732984965886</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N5" t="n">
-        <v>1096.663422488788</v>
+        <v>442.1004455070212</v>
       </c>
       <c r="O5" t="n">
         <v>823.0581258554995</v>
       </c>
       <c r="P5" t="n">
-        <v>287.454101260672</v>
+        <v>757.9603816487216</v>
       </c>
       <c r="Q5" t="n">
         <v>151.5505285485909</v>
@@ -8444,16 +8444,16 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>683.0753298888548</v>
       </c>
       <c r="M8" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N8" t="n">
-        <v>956.6806265221425</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O8" t="n">
-        <v>823.0581258554995</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -8675,28 +8675,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>18.32415699885917</v>
+        <v>266.036495558913</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L11" t="n">
-        <v>754.9143015075377</v>
+        <v>754.9143015075376</v>
       </c>
       <c r="M11" t="n">
-        <v>509.6732984965886</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
-        <v>706.9841039229354</v>
+        <v>442.1004455070212</v>
       </c>
       <c r="O11" t="n">
-        <v>823.0581258554995</v>
+        <v>37.05812585549948</v>
       </c>
       <c r="P11" t="n">
         <v>757.9603816487216</v>
       </c>
       <c r="Q11" t="n">
-        <v>615.8520732695737</v>
+        <v>151.5505285485909</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8915,19 +8915,19 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>562.6064421290152</v>
+        <v>754.9143015075376</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N14" t="n">
-        <v>442.1004455070212</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
-        <v>823.0581258554995</v>
+        <v>693.0624070183095</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -9155,7 +9155,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
-        <v>754.9143015075376</v>
+        <v>641.7225000135636</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
@@ -9164,13 +9164,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>388.1678690825079</v>
+        <v>37.05812585549948</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>151.5505285485909</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,7 +9386,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>18.32415699885917</v>
       </c>
       <c r="K20" t="n">
         <v>716.8751175230994</v>
@@ -9398,16 +9398,16 @@
         <v>509.6732984965886</v>
       </c>
       <c r="N20" t="n">
-        <v>830.3895474931167</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O20" t="n">
-        <v>37.05812585549948</v>
+        <v>477.4236673748649</v>
       </c>
       <c r="P20" t="n">
-        <v>758.9603816487216</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>151.5505285485909</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,13 +9623,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>18.32415699885917</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L23" t="n">
-        <v>280.8983765685166</v>
+        <v>233.7015163858619</v>
       </c>
       <c r="M23" t="n">
         <v>1060.271045550332</v>
@@ -9638,13 +9638,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>824.0581258555009</v>
+        <v>37.05812585549948</v>
       </c>
       <c r="P23" t="n">
-        <v>758.960381648723</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>151.5505285485909</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,28 +9860,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>18.32415699885917</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>657.9427788944723</v>
+        <v>538.7786541110854</v>
       </c>
       <c r="L26" t="n">
-        <v>651.9143015075376</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>518.8671205060343</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>720.0581258555046</v>
+        <v>37.05812585549948</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>151.5505285485909</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10097,28 +10097,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>18.32415699885917</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>657.9427788944723</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>651.9143015075376</v>
+        <v>651.914301507564</v>
       </c>
       <c r="M29" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
-        <v>442.1004455070212</v>
+        <v>764.8293198132242</v>
       </c>
       <c r="O29" t="n">
-        <v>332.5232561335353</v>
+        <v>720.0581258555089</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>151.5505285485909</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,22 +10334,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>317.1690891896006</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>651.9143015075376</v>
+        <v>406.3764011647833</v>
       </c>
       <c r="M32" t="n">
-        <v>1060.271045550332</v>
+        <v>509.6732984965886</v>
       </c>
       <c r="N32" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
-        <v>37.05812585549948</v>
+        <v>720.0581258555162</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -10574,25 +10574,25 @@
         <v>18.32415699885917</v>
       </c>
       <c r="K35" t="n">
-        <v>657.9427788944723</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>651.914301507564</v>
       </c>
       <c r="M35" t="n">
-        <v>509.6732984965886</v>
+        <v>675.7185730741487</v>
       </c>
       <c r="N35" t="n">
-        <v>1066.418787418591</v>
+        <v>442.1004455070212</v>
       </c>
       <c r="O35" t="n">
-        <v>720.0581258555037</v>
+        <v>720.0581258555235</v>
       </c>
       <c r="P35" t="n">
-        <v>654.9603816487258</v>
+        <v>654.9603816487456</v>
       </c>
       <c r="Q35" t="n">
-        <v>151.5505285485909</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10808,25 +10808,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>18.32415699885917</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>657.9427788944723</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>651.9143015075376</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>509.6732984965886</v>
+        <v>915.6522949944004</v>
       </c>
       <c r="N38" t="n">
-        <v>605.1633228387965</v>
+        <v>442.1004455070212</v>
       </c>
       <c r="O38" t="n">
-        <v>720.0581258555037</v>
+        <v>720.0581258555308</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>654.9603816487529</v>
       </c>
       <c r="Q38" t="n">
         <v>615.8520732695737</v>
@@ -11045,28 +11045,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>18.32415699885917</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>630.7442239654637</v>
+        <v>538.3812494440917</v>
       </c>
       <c r="L41" t="n">
-        <v>651.9143015075376</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>509.6732984965886</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>1096.663422488788</v>
+        <v>442.1004455070212</v>
       </c>
       <c r="O41" t="n">
-        <v>720.0581258555037</v>
+        <v>37.05812585549948</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>654.9603816487602</v>
       </c>
       <c r="Q41" t="n">
-        <v>151.5505285485909</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11285,25 +11285,25 @@
         <v>18.32415699885917</v>
       </c>
       <c r="K44" t="n">
-        <v>656.9427788944723</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>650.7957689702109</v>
+        <v>650.914301507564</v>
       </c>
       <c r="M44" t="n">
-        <v>509.6732984965886</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>1096.663422488788</v>
+        <v>710.5487587199846</v>
       </c>
       <c r="O44" t="n">
-        <v>37.05812585549948</v>
+        <v>719.0581258555258</v>
       </c>
       <c r="P44" t="n">
-        <v>653.960381648726</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>151.5505285485909</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -23238,7 +23238,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>183.5291709009383</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -23277,22 +23277,22 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>368.8132802210262</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>432.2055377546408</v>
       </c>
       <c r="V11" t="n">
-        <v>327.885829212414</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>375.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>294.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -23475,7 +23475,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>164.5603873623931</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -23511,7 +23511,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>251.3593738324737</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -23520,16 +23520,16 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>275.6430661352996</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>400.3734759809475</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>245.5920363644425</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -23618,22 +23618,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>48.11380033707866</v>
+        <v>49.11380033707866</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>46.53621805555548</v>
+        <v>47.53621805555548</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>42.98090483695654</v>
       </c>
       <c r="F16" t="n">
-        <v>35.38285596774193</v>
+        <v>36.38285596774193</v>
       </c>
       <c r="G16" t="n">
-        <v>5.955512185792327</v>
+        <v>6.955512185792327</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -23645,31 +23645,31 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>39.25487216179878</v>
+        <v>40.25487216179878</v>
       </c>
       <c r="L16" t="n">
-        <v>171.410808485648</v>
+        <v>172.410808485648</v>
       </c>
       <c r="M16" t="n">
-        <v>267.7806769763204</v>
+        <v>268.7806769763204</v>
       </c>
       <c r="N16" t="n">
-        <v>318.6634851077505</v>
+        <v>319.6634851077505</v>
       </c>
       <c r="O16" t="n">
-        <v>388.9561870298346</v>
+        <v>389.9561870298346</v>
       </c>
       <c r="P16" t="n">
-        <v>245.4089855868819</v>
+        <v>438.7610776561463</v>
       </c>
       <c r="Q16" t="n">
-        <v>479.440266425598</v>
+        <v>84.66902221296078</v>
       </c>
       <c r="R16" t="n">
-        <v>483.6291115877085</v>
+        <v>484.6291115877085</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>122.8335944569538</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23687,7 +23687,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>49.46535284946236</v>
       </c>
     </row>
     <row r="17">
@@ -23748,7 +23748,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.511797559309059</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -23757,7 +23757,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>3.511797559308832</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -23855,7 +23855,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1.113800337078658</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -23888,25 +23888,25 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>220.7806769763204</v>
       </c>
       <c r="N19" t="n">
-        <v>271.6634851077505</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>341.9561870298346</v>
+        <v>318.9933145513497</v>
       </c>
       <c r="P19" t="n">
-        <v>284.8747916958077</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>432.440266425598</v>
       </c>
       <c r="R19" t="n">
         <v>436.6291115877085</v>
       </c>
       <c r="S19" t="n">
-        <v>74.83359445695379</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -24122,7 +24122,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>68.282959881598</v>
+        <v>49.90898263014029</v>
       </c>
       <c r="M22" t="n">
         <v>220.7806769763204</v>
@@ -24131,7 +24131,7 @@
         <v>271.6634851077505</v>
       </c>
       <c r="O22" t="n">
-        <v>341.9561870298346</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -24140,10 +24140,10 @@
         <v>432.440266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>436.6291115877084</v>
       </c>
       <c r="S22" t="n">
-        <v>74.83359445695379</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24161,7 +24161,7 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.465352849462363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -24329,7 +24329,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>1.113800337078658</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -24368,19 +24368,19 @@
         <v>271.6634851077505</v>
       </c>
       <c r="O25" t="n">
-        <v>341.9561870298346</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>390.7610776561463</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>60.38493462235544</v>
+        <v>280.5256929265955</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>436.6291115877084</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>74.83359445695379</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24408,25 +24408,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>264.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>232.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>193.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>128.4711215999922</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>187.8896287080119</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>188.9922868442309</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24456,16 +24456,16 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>21.50474455693768</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>273.3593738324736</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>368.8132802210262</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>432.2055377546408</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -24474,10 +24474,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>375.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>114.1470303159925</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -24502,7 +24502,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>3.711026554574617</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -24535,7 +24535,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.71102655447271</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -24602,7 +24602,7 @@
         <v>289.7806769763204</v>
       </c>
       <c r="N28" t="n">
-        <v>340.6634851077505</v>
+        <v>35.83036973297214</v>
       </c>
       <c r="O28" t="n">
         <v>410.9561870298346</v>
@@ -24611,7 +24611,7 @@
         <v>459.7610776561463</v>
       </c>
       <c r="Q28" t="n">
-        <v>276.4453137389917</v>
+        <v>501.440266425598</v>
       </c>
       <c r="R28" t="n">
         <v>505.6291115877085</v>
@@ -24629,13 +24629,13 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>9.372809838709685</v>
       </c>
       <c r="X28" t="n">
         <v>30.44364543010755</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>70.46535284946236</v>
       </c>
     </row>
     <row r="29">
@@ -24645,19 +24645,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>204.9993129555745</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>86.0627353906298</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>127.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -24708,10 +24708,10 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>324.2348846036907</v>
       </c>
       <c r="X29" t="n">
-        <v>315.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -24803,16 +24803,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>10.11380033707866</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>8.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>3.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -24836,16 +24836,16 @@
         <v>133.410808485648</v>
       </c>
       <c r="M31" t="n">
-        <v>229.7806769763204</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>280.6634851077505</v>
+        <v>193.953226026578</v>
       </c>
       <c r="O31" t="n">
         <v>350.9561870298346</v>
       </c>
       <c r="P31" t="n">
-        <v>164.7004135001737</v>
+        <v>399.7610776561463</v>
       </c>
       <c r="Q31" t="n">
         <v>441.440266425598</v>
@@ -24854,7 +24854,7 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>83.83359445695379</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -24888,19 +24888,19 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>133.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>127.3632896068686</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>126.5603873623931</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>128.9922868442309</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -24942,13 +24942,13 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>352.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>43.04401765263572</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>146.3182337457436</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -25046,7 +25046,7 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>8.53621805555548</v>
       </c>
       <c r="E34" t="n">
         <v>3.98090483695654</v>
@@ -25073,7 +25073,7 @@
         <v>133.410808485648</v>
       </c>
       <c r="M34" t="n">
-        <v>229.7806769763204</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -25082,16 +25082,16 @@
         <v>350.9561870298346</v>
       </c>
       <c r="P34" t="n">
-        <v>399.7610776561463</v>
+        <v>145.6818695395825</v>
       </c>
       <c r="Q34" t="n">
-        <v>49.95019384522305</v>
+        <v>441.440266425598</v>
       </c>
       <c r="R34" t="n">
         <v>445.6291115877085</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>83.83359445695379</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25119,10 +25119,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>204.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>172.4745782429939</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -25134,7 +25134,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>8.953051143066986</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -25170,13 +25170,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>213.3593738324736</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>143.4002454837395</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -25185,7 +25185,7 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>315.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -25277,16 +25277,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>8.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>3.98090483695654</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -25313,16 +25313,16 @@
         <v>229.7806769763204</v>
       </c>
       <c r="N37" t="n">
-        <v>271.1898369424368</v>
+        <v>280.6634851077505</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>399.7610776561463</v>
       </c>
       <c r="Q37" t="n">
-        <v>441.440266425598</v>
+        <v>36.40930131035333</v>
       </c>
       <c r="R37" t="n">
         <v>445.6291115877084</v>
@@ -25346,7 +25346,7 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>10.46535284946236</v>
       </c>
     </row>
     <row r="38">
@@ -25356,7 +25356,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>84.96007725430877</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -25413,7 +25413,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>84.96007725441086</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -25520,7 +25520,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>8.53621805555548</v>
       </c>
       <c r="E40" t="n">
         <v>3.98090483695654</v>
@@ -25541,28 +25541,28 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>1.254872161798778</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>133.410808485648</v>
       </c>
       <c r="M40" t="n">
-        <v>229.7806769763204</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>50.30174635760676</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>350.9561870298346</v>
+        <v>182.3169980444071</v>
       </c>
       <c r="P40" t="n">
         <v>399.7610776561463</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>441.440266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>445.6291115877085</v>
+        <v>445.6291115877084</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -25593,10 +25593,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>352.9993129555745</v>
+        <v>260.4263432972006</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>320.4745782429939</v>
       </c>
       <c r="D41" t="n">
         <v>281.3391557398498</v>
@@ -25608,13 +25608,13 @@
         <v>275.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>274.5603873623931</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>276.9922868442309</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>13.48689837615197</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25641,28 +25641,28 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>109.5047445569377</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>361.3593738324736</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>451.4427160357973</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>520.2055377546408</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>500.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>509.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>382.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -25675,25 +25675,25 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>95.65199533385947</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>213.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>210.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>196.6341396486123</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>202.1501815260438</v>
       </c>
       <c r="I42" t="n">
-        <v>84.49761230644287</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25717,10 +25717,10 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>30.62552924142297</v>
       </c>
       <c r="R42" t="n">
-        <v>411.7299859716246</v>
+        <v>190.2935117851549</v>
       </c>
       <c r="S42" t="n">
         <v>335.606311285366</v>
@@ -25732,16 +25732,16 @@
         <v>271.2034257979226</v>
       </c>
       <c r="V42" t="n">
-        <v>285.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>303.3731429098285</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>290.8627394453875</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>270.3913927661343</v>
       </c>
     </row>
     <row r="43">
@@ -25769,10 +25769,10 @@
         <v>115.9555121857923</v>
       </c>
       <c r="H43" t="n">
-        <v>98.98551954424157</v>
+        <v>98.98551954424158</v>
       </c>
       <c r="I43" t="n">
-        <v>44.97620971847893</v>
+        <v>44.97620971847891</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -25805,16 +25805,16 @@
         <v>231.8335944569538</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>80.64702552265115</v>
       </c>
       <c r="U43" t="n">
-        <v>21.95357160232679</v>
+        <v>21.9535716023268</v>
       </c>
       <c r="V43" t="n">
-        <v>70.17031021621619</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>80.03125101215535</v>
+        <v>69.55453570572038</v>
       </c>
       <c r="X43" t="n">
         <v>118.4436454301076</v>
@@ -25830,28 +25830,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>434.9993129555745</v>
+        <v>433.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>60.51526639291706</v>
       </c>
       <c r="D44" t="n">
-        <v>363.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>357.3632896068686</v>
+        <v>356.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>357.8896287080119</v>
+        <v>356.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>356.5603873623931</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>358.9922868442309</v>
+        <v>357.9922868442309</v>
       </c>
       <c r="I44" t="n">
-        <v>95.48689837615197</v>
+        <v>94.48689837615194</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -25878,28 +25878,28 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>29.1750294629835</v>
+        <v>190.5047445569377</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>538.8132802210262</v>
+        <v>537.8132802210262</v>
       </c>
       <c r="U44" t="n">
-        <v>602.2055377546408</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>581.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>590.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>545.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>463.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -25909,25 +25909,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>337.5565566463266</v>
+        <v>336.5565566463266</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>300.9376868977026</v>
+        <v>299.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>295.6720972219126</v>
+        <v>294.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>291.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>277.6341396486122</v>
       </c>
       <c r="H45" t="n">
-        <v>284.1501815260438</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -25954,31 +25954,31 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>112.625529241423</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>493.7299859716246</v>
+        <v>492.7299859716246</v>
       </c>
       <c r="S45" t="n">
-        <v>417.606311285366</v>
+        <v>416.606311285366</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>356.9329444627969</v>
       </c>
       <c r="U45" t="n">
-        <v>353.2034257979226</v>
+        <v>28.57556873656029</v>
       </c>
       <c r="V45" t="n">
-        <v>367.5106671915202</v>
+        <v>366.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>385.3731429098285</v>
+        <v>384.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>239.6524090732947</v>
+        <v>371.8627394453875</v>
       </c>
       <c r="Y45" t="n">
-        <v>352.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -25988,76 +25988,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>240.1138003370787</v>
+        <v>239.1138003370787</v>
       </c>
       <c r="C46" t="n">
-        <v>225.7252466480447</v>
+        <v>224.7252466480447</v>
       </c>
       <c r="D46" t="n">
-        <v>238.5362180555555</v>
+        <v>237.5362180555555</v>
       </c>
       <c r="E46" t="n">
-        <v>233.9809048369565</v>
+        <v>232.9809048369565</v>
       </c>
       <c r="F46" t="n">
-        <v>227.3828559677419</v>
+        <v>226.3828559677419</v>
       </c>
       <c r="G46" t="n">
-        <v>197.9555121857923</v>
+        <v>196.9555121857923</v>
       </c>
       <c r="H46" t="n">
-        <v>180.9855195442416</v>
+        <v>179.9855195442416</v>
       </c>
       <c r="I46" t="n">
-        <v>126.9762097184789</v>
+        <v>107.3757253692734</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>231.2548721617988</v>
+        <v>230.2548721617988</v>
       </c>
       <c r="L46" t="n">
-        <v>363.410808485648</v>
+        <v>362.410808485648</v>
       </c>
       <c r="M46" t="n">
-        <v>459.7806769763204</v>
+        <v>458.7806769763204</v>
       </c>
       <c r="N46" t="n">
-        <v>510.6634851077505</v>
+        <v>509.6634851077505</v>
       </c>
       <c r="O46" t="n">
-        <v>580.9561870298346</v>
+        <v>579.9561870298346</v>
       </c>
       <c r="P46" t="n">
-        <v>629.7610776561463</v>
+        <v>628.7610776561463</v>
       </c>
       <c r="Q46" t="n">
-        <v>671.440266425598</v>
+        <v>670.440266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>675.6291115877084</v>
+        <v>674.6291115877084</v>
       </c>
       <c r="S46" t="n">
-        <v>313.8335944569538</v>
+        <v>312.8335944569538</v>
       </c>
       <c r="T46" t="n">
-        <v>145.0266411734457</v>
+        <v>161.6470255226511</v>
       </c>
       <c r="U46" t="n">
-        <v>103.9535716023268</v>
+        <v>102.9535716023268</v>
       </c>
       <c r="V46" t="n">
-        <v>152.1703102162162</v>
+        <v>151.1703102162162</v>
       </c>
       <c r="W46" t="n">
-        <v>179.3728098387097</v>
+        <v>178.3728098387097</v>
       </c>
       <c r="X46" t="n">
-        <v>200.4436454301076</v>
+        <v>199.4436454301076</v>
       </c>
       <c r="Y46" t="n">
-        <v>240.4653528494624</v>
+        <v>239.4653528494624</v>
       </c>
     </row>
   </sheetData>
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5257562.311672703</v>
+        <v>5256094.162375981</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6299002.168268903</v>
+        <v>6297534.018972179</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7340766.308643518</v>
+        <v>7339298.159346794</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8382443.773462578</v>
+        <v>8380975.624165853</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9287329.042209378</v>
+        <v>9285860.892912665</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10288837.68130246</v>
+        <v>10287369.53200575</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11290346.32039555</v>
+        <v>11288878.17109885</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12291854.95948864</v>
+        <v>12290386.81019195</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>13293363.59858174</v>
+        <v>13291895.44928505</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13998309.23786508</v>
+        <v>13996841.08856839</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14507878.77596886</v>
+        <v>14508789.00290018</v>
       </c>
     </row>
   </sheetData>
@@ -26278,40 +26278,40 @@
         <v>1133439.336299335</v>
       </c>
       <c r="E2" t="n">
-        <v>996436.0477118184</v>
+        <v>996436.047711818</v>
       </c>
       <c r="F2" t="n">
-        <v>1031389.12307618</v>
+        <v>1029834.61205612</v>
       </c>
       <c r="G2" t="n">
         <v>1102701.024631272</v>
       </c>
       <c r="H2" t="n">
-        <v>1102952.609808421</v>
+        <v>1102952.609808422</v>
       </c>
       <c r="I2" t="n">
         <v>1102952.609808421</v>
       </c>
       <c r="J2" t="n">
-        <v>967658.3222024958</v>
+        <v>967658.3222025069</v>
       </c>
       <c r="K2" t="n">
-        <v>1060420.911980918</v>
+        <v>1060420.911980921</v>
       </c>
       <c r="L2" t="n">
-        <v>1060420.911980918</v>
+        <v>1060420.911980923</v>
       </c>
       <c r="M2" t="n">
-        <v>1060420.911980916</v>
+        <v>1060420.911980924</v>
       </c>
       <c r="N2" t="n">
-        <v>1060420.911980918</v>
+        <v>1060420.911980924</v>
       </c>
       <c r="O2" t="n">
-        <v>746413.0298294041</v>
+        <v>746413.0298294118</v>
       </c>
       <c r="P2" t="n">
-        <v>539635.9909334047</v>
+        <v>542154.2716454113</v>
       </c>
     </row>
     <row r="3">
@@ -26333,10 +26333,10 @@
         <v>173600</v>
       </c>
       <c r="F3" t="n">
-        <v>17600</v>
+        <v>16800</v>
       </c>
       <c r="G3" t="n">
-        <v>37600</v>
+        <v>38400</v>
       </c>
       <c r="H3" t="n">
         <v>352</v>
@@ -26345,13 +26345,13 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>358464</v>
+        <v>358464.0000000093</v>
       </c>
       <c r="K3" t="n">
-        <v>65600</v>
+        <v>64800</v>
       </c>
       <c r="L3" t="n">
-        <v>37600</v>
+        <v>38400</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>565203.8302212236</v>
+        <v>569786.2549648401</v>
       </c>
       <c r="C4" t="n">
-        <v>563457.7657068542</v>
+        <v>568040.1904504707</v>
       </c>
       <c r="D4" t="n">
-        <v>561709.3325469894</v>
+        <v>566291.7572906059</v>
       </c>
       <c r="E4" t="n">
-        <v>474083.6578175171</v>
+        <v>478662.7959448834</v>
       </c>
       <c r="F4" t="n">
-        <v>494432.555328802</v>
+        <v>498044.1295530464</v>
       </c>
       <c r="G4" t="n">
-        <v>537171.0106916493</v>
+        <v>541750.1488190156</v>
       </c>
       <c r="H4" t="n">
-        <v>535561.4640450518</v>
+        <v>540143.6323398908</v>
       </c>
       <c r="I4" t="n">
-        <v>533880.0794923378</v>
+        <v>538462.2477871766</v>
       </c>
       <c r="J4" t="n">
-        <v>458101.2204919368</v>
+        <v>462368.2513696422</v>
       </c>
       <c r="K4" t="n">
-        <v>513252.9762882265</v>
+        <v>517520.0071659283</v>
       </c>
       <c r="L4" t="n">
-        <v>511599.5158273155</v>
+        <v>515866.5467050178</v>
       </c>
       <c r="M4" t="n">
-        <v>509943.6921233343</v>
+        <v>514210.7230010373</v>
       </c>
       <c r="N4" t="n">
-        <v>508285.487620206</v>
+        <v>512552.518497909</v>
       </c>
       <c r="O4" t="n">
-        <v>317158.0882001875</v>
+        <v>321425.1190778905</v>
       </c>
       <c r="P4" t="n">
-        <v>191960.4429978536</v>
+        <v>197739.8757526973</v>
       </c>
     </row>
     <row r="5">
@@ -26437,7 +26437,7 @@
         <v>67099.973</v>
       </c>
       <c r="F5" t="n">
-        <v>68949.49099999999</v>
+        <v>68865.42199999999</v>
       </c>
       <c r="G5" t="n">
         <v>72900.734</v>
@@ -26449,25 +26449,25 @@
         <v>72961.534</v>
       </c>
       <c r="J5" t="n">
-        <v>60837.573</v>
+        <v>60837.5730000016</v>
       </c>
       <c r="K5" t="n">
-        <v>65881.713</v>
+        <v>65881.71300000159</v>
       </c>
       <c r="L5" t="n">
-        <v>65881.713</v>
+        <v>65881.71300000159</v>
       </c>
       <c r="M5" t="n">
-        <v>65881.713</v>
+        <v>65881.71300000159</v>
       </c>
       <c r="N5" t="n">
-        <v>65881.713</v>
+        <v>65881.71300000159</v>
       </c>
       <c r="O5" t="n">
-        <v>53439.501</v>
+        <v>53439.5010000016</v>
       </c>
       <c r="P5" t="n">
-        <v>46485.043</v>
+        <v>46569.11200000159</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>161303.9060781115</v>
+        <v>156721.481334495</v>
       </c>
       <c r="C6" t="n">
-        <v>487496.970592481</v>
+        <v>482914.5458488642</v>
       </c>
       <c r="D6" t="n">
-        <v>489245.4037523455</v>
+        <v>484662.9790087295</v>
       </c>
       <c r="E6" t="n">
-        <v>281652.4168943013</v>
+        <v>277073.2787669346</v>
       </c>
       <c r="F6" t="n">
-        <v>450407.0767473776</v>
+        <v>446125.0605030737</v>
       </c>
       <c r="G6" t="n">
-        <v>455029.2799396226</v>
+        <v>449650.1418122565</v>
       </c>
       <c r="H6" t="n">
-        <v>494077.6117633689</v>
+        <v>489495.4434685309</v>
       </c>
       <c r="I6" t="n">
-        <v>496110.9963160835</v>
+        <v>491528.8280212444</v>
       </c>
       <c r="J6" t="n">
-        <v>90255.52871055898</v>
+        <v>85988.49783285381</v>
       </c>
       <c r="K6" t="n">
-        <v>415686.2226926911</v>
+        <v>412219.1918149913</v>
       </c>
       <c r="L6" t="n">
-        <v>445339.6831536022</v>
+        <v>440272.6522759038</v>
       </c>
       <c r="M6" t="n">
-        <v>484595.506857582</v>
+        <v>480328.4759798853</v>
       </c>
       <c r="N6" t="n">
-        <v>486253.7113607116</v>
+        <v>481986.6804830136</v>
       </c>
       <c r="O6" t="n">
-        <v>375815.4406292166</v>
+        <v>371548.4097515196</v>
       </c>
       <c r="P6" t="n">
-        <v>301190.504935551</v>
+        <v>297845.2838927124</v>
       </c>
     </row>
   </sheetData>
@@ -26767,7 +26767,7 @@
         <v>217</v>
       </c>
       <c r="F2" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G2" t="n">
         <v>286</v>
@@ -26797,7 +26797,7 @@
         <v>129</v>
       </c>
       <c r="P2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -26883,25 +26883,25 @@
         <v>787</v>
       </c>
       <c r="J4" t="n">
-        <v>683</v>
+        <v>683.0000000000263</v>
       </c>
       <c r="K4" t="n">
-        <v>683</v>
+        <v>683.0000000000263</v>
       </c>
       <c r="L4" t="n">
-        <v>683</v>
+        <v>683.0000000000263</v>
       </c>
       <c r="M4" t="n">
-        <v>683</v>
+        <v>683.0000000000263</v>
       </c>
       <c r="N4" t="n">
-        <v>683</v>
+        <v>683.0000000000263</v>
       </c>
       <c r="O4" t="n">
-        <v>683</v>
+        <v>683.0000000000263</v>
       </c>
       <c r="P4" t="n">
-        <v>682</v>
+        <v>682.0000000000263</v>
       </c>
     </row>
   </sheetData>
@@ -26984,31 +26984,31 @@
         <v>217</v>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
         <v>148</v>
       </c>
       <c r="K2" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>-0</v>
@@ -27100,7 +27100,7 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>682</v>
+        <v>682.0000000000193</v>
       </c>
       <c r="K4" t="n">
         <v>-0</v>
@@ -27216,10 +27216,10 @@
         <v>217</v>
       </c>
       <c r="K2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -27231,7 +27231,7 @@
         <v>148</v>
       </c>
       <c r="P2" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3">
@@ -27433,7 +27433,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>400</v>
@@ -27442,13 +27442,13 @@
         <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>388.5034404923986</v>
       </c>
       <c r="F2" t="n">
         <v>400</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H2" t="n">
         <v>400</v>
@@ -27481,10 +27481,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>238.5047445569377</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27499,10 +27499,10 @@
         <v>400</v>
       </c>
       <c r="X2" t="n">
-        <v>149.998695935461</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -27515,7 +27515,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
@@ -27527,13 +27527,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.6341396486122</v>
+        <v>85.88659404607424</v>
       </c>
       <c r="H3" t="n">
         <v>331.1501815260438</v>
       </c>
       <c r="I3" t="n">
-        <v>213.4976123064429</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27569,7 +27569,7 @@
         <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>307.8547545365383</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
@@ -27578,7 +27578,7 @@
         <v>400</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y3" t="n">
         <v>399.3913927661343</v>
@@ -27597,7 +27597,7 @@
         <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
         <v>280.9809048369565</v>
@@ -27606,16 +27606,16 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
-        <v>400</v>
+        <v>244.9555121857923</v>
       </c>
       <c r="H4" t="n">
         <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>173.9762097184789</v>
+        <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>51.92765605674532</v>
+        <v>152.7358038186109</v>
       </c>
       <c r="K4" t="n">
         <v>400</v>
@@ -27642,13 +27642,13 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>360.8335944569538</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
         <v>209.6470255226511</v>
       </c>
       <c r="U4" t="n">
-        <v>400</v>
+        <v>150.9535716023268</v>
       </c>
       <c r="V4" t="n">
         <v>400</v>
@@ -27657,7 +27657,7 @@
         <v>400</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y4" t="n">
         <v>400</v>
@@ -27670,28 +27670,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>246.0165421162467</v>
+        <v>400</v>
       </c>
       <c r="C5" t="n">
         <v>400</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>142.486898376152</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27721,10 +27721,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
+        <v>388.5034404923984</v>
+      </c>
+      <c r="T5" t="n">
         <v>400</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>400</v>
@@ -27749,13 +27749,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>96.1669121928181</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
@@ -27800,7 +27800,7 @@
         <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
@@ -27809,13 +27809,13 @@
         <v>400</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="W6" t="n">
         <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>171.6858694959227</v>
+        <v>400</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27828,7 +27828,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
         <v>272.7252466480447</v>
@@ -27840,19 +27840,19 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
-        <v>323.1285693581652</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
+        <v>244.9555121857923</v>
+      </c>
+      <c r="H7" t="n">
+        <v>227.9855195442416</v>
+      </c>
+      <c r="I7" t="n">
+        <v>173.9762097184789</v>
+      </c>
+      <c r="J7" t="n">
         <v>400</v>
-      </c>
-      <c r="H7" t="n">
-        <v>400</v>
-      </c>
-      <c r="I7" t="n">
-        <v>400</v>
-      </c>
-      <c r="J7" t="n">
-        <v>29.02185047525202</v>
       </c>
       <c r="K7" t="n">
         <v>400</v>
@@ -27885,19 +27885,19 @@
         <v>400</v>
       </c>
       <c r="U7" t="n">
+        <v>277.81583057587</v>
+      </c>
+      <c r="V7" t="n">
         <v>400</v>
-      </c>
-      <c r="V7" t="n">
-        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
         <v>400</v>
       </c>
       <c r="X7" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27916,49 +27916,49 @@
         <v>400</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F8" t="n">
-        <v>149.998695935461</v>
+        <v>388.5034404923986</v>
       </c>
       <c r="G8" t="n">
         <v>400</v>
       </c>
       <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>400</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>238.5047445569377</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -27970,7 +27970,7 @@
         <v>400</v>
       </c>
       <c r="W8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>400</v>
@@ -27992,22 +27992,22 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>55.43554972012095</v>
       </c>
       <c r="F9" t="n">
-        <v>288.2008543916185</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>325.6341396486122</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>331.1501815260438</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>213.4976123064429</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28034,13 +28034,13 @@
         <v>159.625529241423</v>
       </c>
       <c r="R9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
@@ -28065,7 +28065,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>345.1327639876592</v>
       </c>
       <c r="C10" t="n">
         <v>400</v>
@@ -28077,13 +28077,13 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>244.9555121857923</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>386.2275332827624</v>
+        <v>227.9855195442416</v>
       </c>
       <c r="I10" t="n">
         <v>173.9762097184789</v>
@@ -28092,7 +28092,7 @@
         <v>29.02185047525202</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>278.2548721617988</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28119,10 +28119,10 @@
         <v>400</v>
       </c>
       <c r="T10" t="n">
-        <v>209.6470255226511</v>
+        <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9535716023268</v>
       </c>
       <c r="V10" t="n">
         <v>400</v>
@@ -28259,13 +28259,13 @@
         <v>217</v>
       </c>
       <c r="N12" t="n">
-        <v>217</v>
+        <v>29.02960245973605</v>
       </c>
       <c r="O12" t="n">
         <v>217</v>
       </c>
       <c r="P12" t="n">
-        <v>29.02960245973617</v>
+        <v>217</v>
       </c>
       <c r="Q12" t="n">
         <v>217</v>
@@ -28381,25 +28381,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C14" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D14" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E14" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F14" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G14" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H14" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I14" t="n">
         <v>142.486898376152</v>
@@ -28429,28 +28429,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>238.5047445569377</v>
+        <v>238</v>
       </c>
       <c r="S14" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="T14" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="U14" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="V14" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="W14" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="X14" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Y14" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="15">
@@ -28460,76 +28460,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C15" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D15" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E15" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F15" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G15" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H15" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I15" t="n">
-        <v>213.4976123064429</v>
+        <v>238</v>
       </c>
       <c r="J15" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L15" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>99.20612421153407</v>
+        <v>15.63382651850651</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="P15" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q15" t="n">
-        <v>159.625529241423</v>
+        <v>238</v>
       </c>
       <c r="R15" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S15" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="T15" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="U15" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="V15" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="W15" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="X15" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Y15" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="16">
@@ -28539,76 +28539,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C16" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D16" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E16" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F16" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G16" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H16" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I16" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J16" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K16" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L16" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M16" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="N16" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O16" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="P16" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q16" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="R16" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S16" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="T16" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="U16" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="V16" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="W16" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="X16" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Y16" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="17">
@@ -28733,16 +28733,16 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>209.517297774965</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>286</v>
-      </c>
-      <c r="O18" t="n">
-        <v>49.89176853354189</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>159.625529241423</v>
       </c>
       <c r="R18" t="n">
         <v>286</v>
@@ -28958,7 +28958,7 @@
         <v>213.4976123064429</v>
       </c>
       <c r="J21" t="n">
-        <v>49.89176853354181</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -28970,16 +28970,16 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
+        <v>209.5172977749648</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>286</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>159.625529241423</v>
       </c>
       <c r="R21" t="n">
         <v>286</v>
@@ -29207,13 +29207,13 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
+        <v>49.89176853354172</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
         <v>286</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>49.89176853354195</v>
       </c>
       <c r="Q24" t="n">
         <v>159.625529241423</v>
@@ -29429,7 +29429,7 @@
         <v>217</v>
       </c>
       <c r="I27" t="n">
-        <v>217</v>
+        <v>213.4976123064429</v>
       </c>
       <c r="J27" t="n">
         <v>217</v>
@@ -29441,13 +29441,13 @@
         <v>217</v>
       </c>
       <c r="M27" t="n">
-        <v>217</v>
+        <v>28.74561472785436</v>
       </c>
       <c r="N27" t="n">
         <v>217</v>
       </c>
       <c r="O27" t="n">
-        <v>25.2432270341933</v>
+        <v>217</v>
       </c>
       <c r="P27" t="n">
         <v>217</v>
@@ -29666,19 +29666,19 @@
         <v>277</v>
       </c>
       <c r="I30" t="n">
+        <v>213.4976123064429</v>
+      </c>
+      <c r="J30" t="n">
+        <v>196.632815365498</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>277</v>
       </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>133.1304276719407</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
-        <v>277</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -29909,19 +29909,19 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>196.6328153654978</v>
+      </c>
+      <c r="O33" t="n">
         <v>277</v>
-      </c>
-      <c r="L33" t="n">
-        <v>196.6328153654978</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -30140,22 +30140,22 @@
         <v>277</v>
       </c>
       <c r="I36" t="n">
-        <v>213.4976123064429</v>
+        <v>277</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>277</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>133.1304276719408</v>
       </c>
       <c r="L36" t="n">
-        <v>277</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>196.6328153654975</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -30383,16 +30383,16 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
+        <v>196.6328153654977</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
         <v>277</v>
-      </c>
-      <c r="L39" t="n">
-        <v>196.6328153654978</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -30620,22 +30620,22 @@
         <v>129</v>
       </c>
       <c r="K42" t="n">
-        <v>63.28301886792453</v>
+        <v>129</v>
       </c>
       <c r="L42" t="n">
         <v>129</v>
       </c>
       <c r="M42" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
         <v>129</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="P42" t="n">
-        <v>129</v>
+        <v>63.28301886792453</v>
       </c>
       <c r="Q42" t="n">
         <v>129</v>
@@ -30751,28 +30751,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C44" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D44" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E44" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F44" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G44" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H44" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I44" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30799,28 +30799,28 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="S44" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="T44" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U44" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V44" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W44" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X44" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Y44" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45">
@@ -30830,76 +30830,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C45" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D45" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E45" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F45" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G45" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H45" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I45" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J45" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K45" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L45" t="n">
-        <v>23.05660377358491</v>
+        <v>48</v>
       </c>
       <c r="M45" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>47</v>
+        <v>23.54716981132075</v>
       </c>
       <c r="O45" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="Q45" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R45" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="S45" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="T45" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U45" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V45" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W45" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X45" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Y45" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="46">
@@ -30909,76 +30909,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="S46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="T46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Y46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -34743,16 +34743,16 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>411.9805795872975</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>741.9323386286271</v>
+        <v>786</v>
       </c>
       <c r="L2" t="n">
-        <v>265.1223229385184</v>
+        <v>161.4794795970406</v>
       </c>
       <c r="M2" t="n">
-        <v>762.1173153852243</v>
+        <v>550.5977470537439</v>
       </c>
       <c r="N2" t="n">
         <v>654.5629769817668</v>
@@ -34761,7 +34761,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>28.03961835127838</v>
+        <v>711.1149482401308</v>
       </c>
       <c r="Q2" t="n">
         <v>464.3015447209827</v>
@@ -34883,7 +34883,7 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -34892,16 +34892,16 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>155.0444878142077</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>172.0144804557584</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>226.0237902815211</v>
       </c>
       <c r="J4" t="n">
-        <v>22.9058055814933</v>
+        <v>123.7139533433589</v>
       </c>
       <c r="K4" t="n">
         <v>121.7451278382012</v>
@@ -34928,13 +34928,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>39.16640554304621</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0464283976732</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>200.8296897837838</v>
@@ -34943,7 +34943,7 @@
         <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
         <v>112.5346471505376</v>
@@ -34980,25 +34980,25 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>411.9805795872975</v>
       </c>
       <c r="K5" t="n">
-        <v>786</v>
+        <v>762.3926714601671</v>
       </c>
       <c r="L5" t="n">
-        <v>786.0000000000002</v>
+        <v>31.08569849246237</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>550.5977470537439</v>
       </c>
       <c r="N5" t="n">
-        <v>654.5629769817668</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>786</v>
       </c>
       <c r="P5" t="n">
-        <v>315.4937196119503</v>
+        <v>786</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -35114,7 +35114,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -35126,19 +35126,19 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>48.74571339042331</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>155.0444878142077</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>172.0144804557584</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>226.0237902815211</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>370.978149524748</v>
       </c>
       <c r="K7" t="n">
         <v>121.7451278382012</v>
@@ -35171,19 +35171,19 @@
         <v>190.3529744773489</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0464283976732</v>
+        <v>126.8622589735432</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
         <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35220,19 +35220,19 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>741.9323386286271</v>
+        <v>786</v>
       </c>
       <c r="L8" t="n">
-        <v>242.6052668239804</v>
+        <v>786.0000000000002</v>
       </c>
       <c r="M8" t="n">
         <v>550.5977470537439</v>
       </c>
       <c r="N8" t="n">
-        <v>514.5801810151213</v>
+        <v>654.5629769817668</v>
       </c>
       <c r="O8" t="n">
-        <v>786</v>
+        <v>58.55480948600895</v>
       </c>
       <c r="P8" t="n">
         <v>28.03961835127838</v>
@@ -35351,7 +35351,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>58.01896365058055</v>
       </c>
       <c r="C10" t="n">
         <v>127.2747533519553</v>
@@ -35363,13 +35363,13 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>155.0444878142077</v>
       </c>
       <c r="H10" t="n">
-        <v>158.2420137385208</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -35378,7 +35378,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>121.7451278382012</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35405,10 +35405,10 @@
         <v>39.1664055430462</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>190.3529744773489</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0464283976732</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>200.8296897837838</v>
@@ -35454,28 +35454,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>247.7123385600538</v>
       </c>
       <c r="K11" t="n">
-        <v>25.05722110552764</v>
+        <v>741.932338628627</v>
       </c>
       <c r="L11" t="n">
         <v>786</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>550.5977470537439</v>
       </c>
       <c r="N11" t="n">
-        <v>264.8836584159143</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>786</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>786</v>
       </c>
       <c r="Q11" t="n">
-        <v>464.3015447209827</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35545,13 +35545,13 @@
         <v>330.6550421645043</v>
       </c>
       <c r="N12" t="n">
-        <v>379.0383519954473</v>
+        <v>191.0679544551833</v>
       </c>
       <c r="O12" t="n">
         <v>483.5334652989728</v>
       </c>
       <c r="P12" t="n">
-        <v>162.821663578163</v>
+        <v>350.7920611184268</v>
       </c>
       <c r="Q12" t="n">
         <v>57.37447075857702</v>
@@ -35694,19 +35694,19 @@
         <v>411.9805795872975</v>
       </c>
       <c r="K14" t="n">
-        <v>741.9323386286271</v>
+        <v>25.05722110552762</v>
       </c>
       <c r="L14" t="n">
-        <v>593.6921406214776</v>
+        <v>786</v>
       </c>
       <c r="M14" t="n">
         <v>550.5977470537439</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>654.5629769817668</v>
       </c>
       <c r="O14" t="n">
-        <v>786</v>
+        <v>656.00428116281</v>
       </c>
       <c r="P14" t="n">
         <v>28.03961835127838</v>
@@ -35767,31 +35767,31 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>24.50238769355713</v>
       </c>
       <c r="J15" t="n">
-        <v>374.1662383131474</v>
+        <v>135.1662383131474</v>
       </c>
       <c r="K15" t="n">
-        <v>447.1230338860744</v>
+        <v>446.1230338860744</v>
       </c>
       <c r="L15" t="n">
-        <v>535.9757621411399</v>
+        <v>534.9757621411399</v>
       </c>
       <c r="M15" t="n">
         <v>113.6550421645043</v>
       </c>
       <c r="N15" t="n">
-        <v>261.2444762069813</v>
+        <v>177.6721785139538</v>
       </c>
       <c r="O15" t="n">
-        <v>266.5334652989728</v>
+        <v>504.5334652989728</v>
       </c>
       <c r="P15" t="n">
-        <v>372.7920611184268</v>
+        <v>371.7920611184268</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>78.37447075857702</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35843,13 +35843,13 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>11.01448045575843</v>
+        <v>10.01448045575843</v>
       </c>
       <c r="I16" t="n">
-        <v>65.02379028152107</v>
+        <v>64.02379028152107</v>
       </c>
       <c r="J16" t="n">
-        <v>209.978149524748</v>
+        <v>208.978149524748</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -35879,16 +35879,16 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>29.35297447734884</v>
+        <v>28.35297447734884</v>
       </c>
       <c r="U16" t="n">
-        <v>88.04642839767321</v>
+        <v>87.04642839767321</v>
       </c>
       <c r="V16" t="n">
-        <v>39.82968978378381</v>
+        <v>38.82968978378381</v>
       </c>
       <c r="W16" t="n">
-        <v>12.62719016129032</v>
+        <v>11.62719016129032</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -35934,7 +35934,7 @@
         <v>741.9323386286271</v>
       </c>
       <c r="L17" t="n">
-        <v>786</v>
+        <v>672.808198506026</v>
       </c>
       <c r="M17" t="n">
         <v>550.5977470537439</v>
@@ -35943,13 +35943,13 @@
         <v>654.5629769817668</v>
       </c>
       <c r="O17" t="n">
-        <v>351.1097432270084</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>28.03961835127838</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>464.3015447209827</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36019,16 +36019,16 @@
         <v>113.6550421645043</v>
       </c>
       <c r="N18" t="n">
-        <v>448.0383519954473</v>
+        <v>162.0383519954473</v>
       </c>
       <c r="O18" t="n">
-        <v>316.4252338325147</v>
+        <v>476.0507630739377</v>
       </c>
       <c r="P18" t="n">
         <v>133.7920611184268</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>126.374470758577</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36165,7 +36165,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>411.9805795872975</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>741.9323386286271</v>
@@ -36177,16 +36177,16 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>388.2891019860955</v>
+        <v>654.5629769817668</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>440.3655415193654</v>
       </c>
       <c r="P20" t="n">
-        <v>787</v>
+        <v>28.03961835127838</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>464.3015447209827</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36244,7 +36244,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>185.0580068466892</v>
+        <v>135.1662383131474</v>
       </c>
       <c r="K21" t="n">
         <v>208.1230338860743</v>
@@ -36256,7 +36256,7 @@
         <v>113.6550421645043</v>
       </c>
       <c r="N21" t="n">
-        <v>448.0383519954473</v>
+        <v>371.5556497704121</v>
       </c>
       <c r="O21" t="n">
         <v>266.5334652989728</v>
@@ -36265,7 +36265,7 @@
         <v>133.7920611184268</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>126.374470758577</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36402,13 +36402,13 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>411.9805795872975</v>
       </c>
       <c r="K23" t="n">
-        <v>25.05722110552763</v>
+        <v>741.9323386286271</v>
       </c>
       <c r="L23" t="n">
-        <v>311.9840750609789</v>
+        <v>264.7872148783242</v>
       </c>
       <c r="M23" t="n">
         <v>550.5977470537439</v>
@@ -36417,13 +36417,13 @@
         <v>654.5629769817668</v>
       </c>
       <c r="O23" t="n">
-        <v>787.0000000000014</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>787.0000000000014</v>
+        <v>28.03961835127838</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>464.3015447209827</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36493,13 +36493,13 @@
         <v>113.6550421645043</v>
       </c>
       <c r="N24" t="n">
-        <v>448.0383519954473</v>
+        <v>211.930120528989</v>
       </c>
       <c r="O24" t="n">
         <v>266.5334652989728</v>
       </c>
       <c r="P24" t="n">
-        <v>183.6838296519688</v>
+        <v>419.7920611184268</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -36639,28 +36639,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>411.9805795872975</v>
       </c>
       <c r="K26" t="n">
-        <v>683</v>
+        <v>563.8358752166132</v>
       </c>
       <c r="L26" t="n">
-        <v>683</v>
+        <v>31.08569849246237</v>
       </c>
       <c r="M26" t="n">
         <v>550.5977470537439</v>
       </c>
       <c r="N26" t="n">
-        <v>76.76667499901319</v>
+        <v>654.5629769817668</v>
       </c>
       <c r="O26" t="n">
-        <v>683.0000000000051</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
         <v>28.03961835127838</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>464.3015447209827</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36715,7 +36715,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>3.502387693557127</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>352.1662383131474</v>
@@ -36727,13 +36727,13 @@
         <v>513.9757621411399</v>
       </c>
       <c r="M27" t="n">
-        <v>330.6550421645043</v>
+        <v>142.4006568923586</v>
       </c>
       <c r="N27" t="n">
         <v>379.0383519954473</v>
       </c>
       <c r="O27" t="n">
-        <v>291.7766923331661</v>
+        <v>483.5334652989728</v>
       </c>
       <c r="P27" t="n">
         <v>350.7920611184268</v>
@@ -36876,28 +36876,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>411.9805795872975</v>
       </c>
       <c r="K29" t="n">
-        <v>683</v>
+        <v>25.05722110552762</v>
       </c>
       <c r="L29" t="n">
-        <v>683</v>
+        <v>683.0000000000263</v>
       </c>
       <c r="M29" t="n">
         <v>550.5977470537439</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>322.728874306203</v>
       </c>
       <c r="O29" t="n">
-        <v>295.4651302780358</v>
+        <v>683.0000000000094</v>
       </c>
       <c r="P29" t="n">
         <v>28.03961835127838</v>
       </c>
       <c r="Q29" t="n">
-        <v>464.3015447209827</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36952,19 +36952,19 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>63.50238769355713</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>135.1662383131474</v>
+        <v>331.7990536786454</v>
       </c>
       <c r="K30" t="n">
-        <v>341.253461558015</v>
+        <v>208.1230338860743</v>
       </c>
       <c r="L30" t="n">
-        <v>296.9757621411399</v>
+        <v>573.9757621411399</v>
       </c>
       <c r="M30" t="n">
-        <v>390.6550421645043</v>
+        <v>113.6550421645043</v>
       </c>
       <c r="N30" t="n">
         <v>162.0383519954473</v>
@@ -37113,22 +37113,22 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>298.8449321907414</v>
+        <v>411.9805795872975</v>
       </c>
       <c r="K32" t="n">
         <v>25.05722110552762</v>
       </c>
       <c r="L32" t="n">
-        <v>683</v>
+        <v>437.4620996572455</v>
       </c>
       <c r="M32" t="n">
-        <v>550.5977470537439</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>654.5629769817668</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>683.0000000000167</v>
       </c>
       <c r="P32" t="n">
         <v>28.03961835127838</v>
@@ -37195,19 +37195,19 @@
         <v>135.1662383131474</v>
       </c>
       <c r="K33" t="n">
-        <v>485.1230338860744</v>
+        <v>208.1230338860743</v>
       </c>
       <c r="L33" t="n">
-        <v>493.6085775066376</v>
+        <v>296.9757621411399</v>
       </c>
       <c r="M33" t="n">
         <v>113.6550421645043</v>
       </c>
       <c r="N33" t="n">
-        <v>162.0383519954473</v>
+        <v>358.671167360945</v>
       </c>
       <c r="O33" t="n">
-        <v>266.5334652989728</v>
+        <v>543.5334652989728</v>
       </c>
       <c r="P33" t="n">
         <v>133.7920611184268</v>
@@ -37353,25 +37353,25 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>683</v>
+        <v>25.05722110552764</v>
       </c>
       <c r="L35" t="n">
-        <v>31.08569849246237</v>
+        <v>683.0000000000263</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>166.04527457756</v>
       </c>
       <c r="N35" t="n">
-        <v>624.3183419115696</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>683.0000000000042</v>
+        <v>683.000000000024</v>
       </c>
       <c r="P35" t="n">
-        <v>683.0000000000042</v>
+        <v>683.000000000024</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>464.3015447209827</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37426,22 +37426,22 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>63.50238769355714</v>
       </c>
       <c r="J36" t="n">
-        <v>135.1662383131474</v>
+        <v>412.1662383131474</v>
       </c>
       <c r="K36" t="n">
-        <v>208.1230338860743</v>
+        <v>341.2534615580151</v>
       </c>
       <c r="L36" t="n">
-        <v>573.9757621411399</v>
+        <v>296.9757621411399</v>
       </c>
       <c r="M36" t="n">
         <v>113.6550421645043</v>
       </c>
       <c r="N36" t="n">
-        <v>358.6711673609448</v>
+        <v>162.0383519954473</v>
       </c>
       <c r="O36" t="n">
         <v>266.5334652989728</v>
@@ -37587,25 +37587,25 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>411.9805795872975</v>
       </c>
       <c r="K38" t="n">
-        <v>683</v>
+        <v>25.05722110552762</v>
       </c>
       <c r="L38" t="n">
-        <v>683</v>
+        <v>31.08569849246226</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>405.9789964978117</v>
       </c>
       <c r="N38" t="n">
-        <v>163.0628773317753</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>683.0000000000042</v>
+        <v>683.0000000000313</v>
       </c>
       <c r="P38" t="n">
-        <v>28.03961835127838</v>
+        <v>683.0000000000313</v>
       </c>
       <c r="Q38" t="n">
         <v>464.3015447209827</v>
@@ -37669,16 +37669,16 @@
         <v>135.1662383131474</v>
       </c>
       <c r="K39" t="n">
-        <v>485.1230338860744</v>
+        <v>404.755849251572</v>
       </c>
       <c r="L39" t="n">
-        <v>493.6085775066376</v>
+        <v>296.9757621411399</v>
       </c>
       <c r="M39" t="n">
         <v>113.6550421645043</v>
       </c>
       <c r="N39" t="n">
-        <v>162.0383519954473</v>
+        <v>439.0383519954473</v>
       </c>
       <c r="O39" t="n">
         <v>266.5334652989728</v>
@@ -37736,10 +37736,10 @@
         <v>2.617144032258068</v>
       </c>
       <c r="G40" t="n">
-        <v>32.04448781420767</v>
+        <v>32.04448781420768</v>
       </c>
       <c r="H40" t="n">
-        <v>49.01448045575843</v>
+        <v>49.01448045575842</v>
       </c>
       <c r="I40" t="n">
         <v>103.0237902815211</v>
@@ -37775,7 +37775,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>67.35297447734884</v>
+        <v>67.35297447734885</v>
       </c>
       <c r="U40" t="n">
         <v>126.0464283976732</v>
@@ -37824,28 +37824,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>411.9805795872975</v>
       </c>
       <c r="K41" t="n">
-        <v>655.8014450709913</v>
+        <v>563.4384705496195</v>
       </c>
       <c r="L41" t="n">
-        <v>683</v>
+        <v>31.08569849246237</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>550.5977470537439</v>
       </c>
       <c r="N41" t="n">
-        <v>654.5629769817668</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>683.0000000000042</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>28.03961835127838</v>
+        <v>683.0000000000385</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>464.3015447209827</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37906,22 +37906,22 @@
         <v>264.1662383131474</v>
       </c>
       <c r="K42" t="n">
-        <v>271.4060527539988</v>
+        <v>337.1230338860743</v>
       </c>
       <c r="L42" t="n">
         <v>425.9757621411399</v>
       </c>
       <c r="M42" t="n">
-        <v>242.6550421645043</v>
+        <v>113.6550421645043</v>
       </c>
       <c r="N42" t="n">
         <v>291.0383519954473</v>
       </c>
       <c r="O42" t="n">
-        <v>266.5334652989728</v>
+        <v>395.5334652989728</v>
       </c>
       <c r="P42" t="n">
-        <v>262.7920611184268</v>
+        <v>197.0750799863513</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -38064,25 +38064,25 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>682</v>
+        <v>25.05722110552764</v>
       </c>
       <c r="L44" t="n">
-        <v>681.8814674626733</v>
+        <v>682.0000000000263</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>550.5977470537439</v>
       </c>
       <c r="N44" t="n">
-        <v>654.5629769817668</v>
+        <v>268.4483132129633</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>682.0000000000263</v>
       </c>
       <c r="P44" t="n">
-        <v>682.0000000000043</v>
+        <v>28.03961835127838</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>464.3015447209827</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38140,25 +38140,25 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>182.1662383131474</v>
+        <v>183.1662383131474</v>
       </c>
       <c r="K45" t="n">
-        <v>255.1230338860743</v>
+        <v>256.1230338860743</v>
       </c>
       <c r="L45" t="n">
-        <v>320.0323659147248</v>
+        <v>344.9757621411399</v>
       </c>
       <c r="M45" t="n">
-        <v>160.6550421645043</v>
+        <v>113.6550421645043</v>
       </c>
       <c r="N45" t="n">
-        <v>209.0383519954473</v>
+        <v>185.585521806768</v>
       </c>
       <c r="O45" t="n">
-        <v>313.5334652989728</v>
+        <v>314.5334652989728</v>
       </c>
       <c r="P45" t="n">
-        <v>133.7920611184268</v>
+        <v>181.7920611184268</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -38219,7 +38219,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>17.97814952474798</v>
+        <v>18.97814952474798</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
